--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128742454</v>
+        <v>128740513</v>
       </c>
       <c r="B4" t="n">
-        <v>90265</v>
+        <v>86753</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2072</v>
+        <v>3712</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716979</v>
+        <v>717090</v>
       </c>
       <c r="R4" t="n">
-        <v>6374541</v>
+        <v>6374531</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -947,24 +947,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Artbestämning bekräftad av Michael Krikorev.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,44 +964,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128740513</v>
+        <v>128742454</v>
       </c>
       <c r="B5" t="n">
-        <v>86753</v>
+        <v>90265</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3712</v>
+        <v>2072</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717090</v>
+        <v>716979</v>
       </c>
       <c r="R5" t="n">
-        <v>6374531</v>
+        <v>6374541</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1059,9 +1044,24 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Artbestämning bekräftad av Michael Krikorev.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,12 +1076,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128740507</v>
+        <v>128738870</v>
       </c>
       <c r="B8" t="n">
-        <v>86949</v>
+        <v>91002</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,21 +1307,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>449</v>
+        <v>1357</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717045</v>
+        <v>716979</v>
       </c>
       <c r="R8" t="n">
-        <v>6374519</v>
+        <v>6374541</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,9 +1364,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1381,65 +1391,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128740488</v>
+        <v>128740507</v>
       </c>
       <c r="B9" t="n">
-        <v>57686</v>
+        <v>86949</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717042</v>
+        <v>717045</v>
       </c>
       <c r="R9" t="n">
-        <v>6374557</v>
+        <v>6374519</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,45 +1500,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128738870</v>
+        <v>128740488</v>
       </c>
       <c r="B10" t="n">
-        <v>91002</v>
+        <v>57686</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1357</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716979</v>
+        <v>717042</v>
       </c>
       <c r="R10" t="n">
-        <v>6374541</v>
+        <v>6374557</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,19 +1576,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,12 +1593,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2407,32 +2407,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128740517</v>
+        <v>128738874</v>
       </c>
       <c r="B19" t="n">
-        <v>86890</v>
+        <v>91002</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3674</v>
+        <v>1357</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716991</v>
+        <v>716987</v>
       </c>
       <c r="R19" t="n">
-        <v>6374571</v>
+        <v>6374546</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2475,9 +2475,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2492,22 +2502,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128738874</v>
+        <v>128740479</v>
       </c>
       <c r="B20" t="n">
-        <v>91002</v>
+        <v>86972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2515,21 +2525,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1357</v>
+        <v>3767</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2539,10 +2549,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>716987</v>
+        <v>717060</v>
       </c>
       <c r="R20" t="n">
-        <v>6374546</v>
+        <v>6374568</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2572,71 +2582,62 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128740479</v>
+        <v>128740517</v>
       </c>
       <c r="B21" t="n">
-        <v>86972</v>
+        <v>86890</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2646,10 +2647,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>717060</v>
+        <v>716991</v>
       </c>
       <c r="R21" t="n">
-        <v>6374568</v>
+        <v>6374571</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2690,7 +2691,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3010,7 +3010,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128740480</v>
+        <v>128738844</v>
       </c>
       <c r="B25" t="n">
         <v>86972</v>
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>716999</v>
+        <v>717061</v>
       </c>
       <c r="R25" t="n">
-        <v>6374513</v>
+        <v>6374502</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3078,9 +3078,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3095,19 +3105,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128738844</v>
+        <v>128740480</v>
       </c>
       <c r="B26" t="n">
         <v>86972</v>
@@ -3142,10 +3152,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>717061</v>
+        <v>716999</v>
       </c>
       <c r="R26" t="n">
-        <v>6374502</v>
+        <v>6374513</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3175,19 +3185,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3202,12 +3202,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3312,32 +3312,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128738872</v>
+        <v>128740496</v>
       </c>
       <c r="B28" t="n">
-        <v>91002</v>
+        <v>86927</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1357</v>
+        <v>6003295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3347,10 +3347,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>716991</v>
+        <v>717083</v>
       </c>
       <c r="R28" t="n">
-        <v>6374537</v>
+        <v>6374544</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3380,46 +3380,37 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>16:03</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>16:03</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128740496</v>
+        <v>128740495</v>
       </c>
       <c r="B29" t="n">
         <v>86927</v>
@@ -3454,10 +3445,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>717083</v>
+        <v>717014</v>
       </c>
       <c r="R29" t="n">
-        <v>6374544</v>
+        <v>6374563</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3517,32 +3508,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128740495</v>
+        <v>128738872</v>
       </c>
       <c r="B30" t="n">
-        <v>86927</v>
+        <v>91002</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6003295</v>
+        <v>1357</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3552,10 +3543,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>717014</v>
+        <v>716991</v>
       </c>
       <c r="R30" t="n">
-        <v>6374563</v>
+        <v>6374537</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3585,30 +3576,39 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -1605,32 +1605,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128742292</v>
+        <v>128740492</v>
       </c>
       <c r="B11" t="n">
-        <v>86890</v>
+        <v>86927</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>717052</v>
+        <v>717123</v>
       </c>
       <c r="R11" t="n">
-        <v>6374546</v>
+        <v>6374559</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,50 +1684,51 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128740492</v>
+        <v>128742292</v>
       </c>
       <c r="B12" t="n">
-        <v>86927</v>
+        <v>86890</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1737,10 +1738,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>717123</v>
+        <v>717052</v>
       </c>
       <c r="R12" t="n">
-        <v>6374559</v>
+        <v>6374546</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1781,19 +1782,18 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2106,10 +2106,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128738871</v>
+        <v>128740483</v>
       </c>
       <c r="B16" t="n">
-        <v>91002</v>
+        <v>86972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2117,21 +2117,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1357</v>
+        <v>3767</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2141,10 +2141,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>716991</v>
+        <v>717059</v>
       </c>
       <c r="R16" t="n">
-        <v>6374543</v>
+        <v>6374495</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2174,19 +2174,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2201,22 +2191,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128740483</v>
+        <v>128738871</v>
       </c>
       <c r="B17" t="n">
-        <v>86972</v>
+        <v>91002</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2224,21 +2214,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3767</v>
+        <v>1357</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2248,10 +2238,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>717059</v>
+        <v>716991</v>
       </c>
       <c r="R17" t="n">
-        <v>6374495</v>
+        <v>6374543</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2281,9 +2271,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2298,12 +2298,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2407,10 +2407,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128738874</v>
+        <v>128740479</v>
       </c>
       <c r="B19" t="n">
-        <v>91002</v>
+        <v>86972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2418,21 +2418,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1357</v>
+        <v>3767</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2442,10 +2442,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716987</v>
+        <v>717060</v>
       </c>
       <c r="R19" t="n">
-        <v>6374546</v>
+        <v>6374568</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2475,71 +2475,62 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128740479</v>
+        <v>128740517</v>
       </c>
       <c r="B20" t="n">
-        <v>86972</v>
+        <v>86890</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2549,10 +2540,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>717060</v>
+        <v>716991</v>
       </c>
       <c r="R20" t="n">
-        <v>6374568</v>
+        <v>6374571</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2593,7 +2584,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2605,39 +2595,39 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128740517</v>
+        <v>128738874</v>
       </c>
       <c r="B21" t="n">
-        <v>86890</v>
+        <v>91002</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3674</v>
+        <v>1357</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2647,10 +2637,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>716991</v>
+        <v>716987</v>
       </c>
       <c r="R21" t="n">
-        <v>6374571</v>
+        <v>6374546</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2680,9 +2670,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2697,12 +2697,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128740515</v>
+        <v>128738869</v>
       </c>
       <c r="B2" t="n">
-        <v>92098</v>
+        <v>86949</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6031</v>
+        <v>449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717022</v>
+        <v>717060</v>
       </c>
       <c r="R2" t="n">
-        <v>6374547</v>
+        <v>6374523</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,9 +743,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,44 +770,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128738869</v>
+        <v>128740515</v>
       </c>
       <c r="B3" t="n">
-        <v>86949</v>
+        <v>92099</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>449</v>
+        <v>6031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717060</v>
+        <v>717022</v>
       </c>
       <c r="R3" t="n">
-        <v>6374523</v>
+        <v>6374547</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -840,19 +850,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,44 +867,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128740513</v>
+        <v>128742454</v>
       </c>
       <c r="B4" t="n">
-        <v>86753</v>
+        <v>90265</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3712</v>
+        <v>2072</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717090</v>
+        <v>716979</v>
       </c>
       <c r="R4" t="n">
-        <v>6374531</v>
+        <v>6374541</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -947,9 +947,24 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Artbestämning bekräftad av Michael Krikorev.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -964,44 +979,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128742454</v>
+        <v>128740513</v>
       </c>
       <c r="B5" t="n">
-        <v>90265</v>
+        <v>86753</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2072</v>
+        <v>3712</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716979</v>
+        <v>717090</v>
       </c>
       <c r="R5" t="n">
-        <v>6374541</v>
+        <v>6374531</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1044,24 +1059,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Artbestämning bekräftad av Michael Krikorev.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,12 +1076,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1299,7 +1299,7 @@
         <v>128738870</v>
       </c>
       <c r="B8" t="n">
-        <v>91002</v>
+        <v>91003</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1605,32 +1605,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128740492</v>
+        <v>128742292</v>
       </c>
       <c r="B11" t="n">
-        <v>86927</v>
+        <v>86890</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>717123</v>
+        <v>717052</v>
       </c>
       <c r="R11" t="n">
-        <v>6374559</v>
+        <v>6374546</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,51 +1684,50 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128742292</v>
+        <v>128740492</v>
       </c>
       <c r="B12" t="n">
-        <v>86890</v>
+        <v>86927</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1738,10 +1737,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>717052</v>
+        <v>717123</v>
       </c>
       <c r="R12" t="n">
-        <v>6374546</v>
+        <v>6374559</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1782,18 +1781,19 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1803,7 +1803,7 @@
         <v>128742260</v>
       </c>
       <c r="B13" t="n">
-        <v>90975</v>
+        <v>90976</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128738888</v>
+        <v>128740483</v>
       </c>
       <c r="B15" t="n">
-        <v>92755</v>
+        <v>86972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2006,37 +2006,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1435</v>
+        <v>3767</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>716959</v>
+        <v>717059</v>
       </c>
       <c r="R15" t="n">
-        <v>6374567</v>
+        <v>6374495</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2066,47 +2063,36 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:58</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:58</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128740483</v>
+        <v>128740481</v>
       </c>
       <c r="B16" t="n">
         <v>86972</v>
@@ -2141,10 +2127,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>717059</v>
+        <v>717052</v>
       </c>
       <c r="R16" t="n">
-        <v>6374495</v>
+        <v>6374557</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2203,10 +2189,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128738871</v>
+        <v>128738874</v>
       </c>
       <c r="B17" t="n">
-        <v>91002</v>
+        <v>91003</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2238,10 +2224,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>716991</v>
+        <v>716987</v>
       </c>
       <c r="R17" t="n">
-        <v>6374543</v>
+        <v>6374546</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2273,7 +2259,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2283,7 +2269,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2310,7 +2296,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128740481</v>
+        <v>128740479</v>
       </c>
       <c r="B18" t="n">
         <v>86972</v>
@@ -2345,10 +2331,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>717052</v>
+        <v>717060</v>
       </c>
       <c r="R18" t="n">
-        <v>6374557</v>
+        <v>6374568</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2389,6 +2375,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2407,32 +2394,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128740479</v>
+        <v>128740517</v>
       </c>
       <c r="B19" t="n">
-        <v>86972</v>
+        <v>86890</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2442,10 +2429,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>717060</v>
+        <v>716991</v>
       </c>
       <c r="R19" t="n">
-        <v>6374568</v>
+        <v>6374571</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2486,7 +2473,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2498,39 +2484,39 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128740517</v>
+        <v>128738868</v>
       </c>
       <c r="B20" t="n">
-        <v>86890</v>
+        <v>86949</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2540,10 +2526,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>716991</v>
+        <v>717048</v>
       </c>
       <c r="R20" t="n">
-        <v>6374571</v>
+        <v>6374524</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2573,9 +2559,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2590,44 +2586,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128738874</v>
+        <v>128742265</v>
       </c>
       <c r="B21" t="n">
-        <v>91002</v>
+        <v>86729</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1357</v>
+        <v>3762</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2637,10 +2633,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>716987</v>
+        <v>717052</v>
       </c>
       <c r="R21" t="n">
-        <v>6374546</v>
+        <v>6374544</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2670,19 +2666,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:34</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2697,44 +2683,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128738868</v>
+        <v>128740490</v>
       </c>
       <c r="B22" t="n">
-        <v>86949</v>
+        <v>86729</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2744,10 +2730,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>717048</v>
+        <v>717075</v>
       </c>
       <c r="R22" t="n">
-        <v>6374524</v>
+        <v>6374568</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2777,19 +2763,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>15:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2804,44 +2780,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128742265</v>
+        <v>128738844</v>
       </c>
       <c r="B23" t="n">
-        <v>86729</v>
+        <v>86972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3762</v>
+        <v>3767</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2851,10 +2827,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>717052</v>
+        <v>717061</v>
       </c>
       <c r="R23" t="n">
-        <v>6374544</v>
+        <v>6374502</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2884,9 +2860,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2901,44 +2887,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128740490</v>
+        <v>128740480</v>
       </c>
       <c r="B24" t="n">
-        <v>86729</v>
+        <v>86972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3762</v>
+        <v>3767</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2948,10 +2934,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>717075</v>
+        <v>716999</v>
       </c>
       <c r="R24" t="n">
-        <v>6374568</v>
+        <v>6374513</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3010,32 +2996,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128738844</v>
+        <v>128740494</v>
       </c>
       <c r="B25" t="n">
-        <v>86972</v>
+        <v>86927</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3767</v>
+        <v>6003295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3045,10 +3031,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>717061</v>
+        <v>716964</v>
       </c>
       <c r="R25" t="n">
-        <v>6374502</v>
+        <v>6374549</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3078,49 +3064,40 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128740480</v>
+        <v>128738872</v>
       </c>
       <c r="B26" t="n">
-        <v>86972</v>
+        <v>91003</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3128,21 +3105,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3767</v>
+        <v>1357</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3152,10 +3129,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>716999</v>
+        <v>716991</v>
       </c>
       <c r="R26" t="n">
-        <v>6374513</v>
+        <v>6374537</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3185,9 +3162,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3202,19 +3189,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128740494</v>
+        <v>128740496</v>
       </c>
       <c r="B27" t="n">
         <v>86927</v>
@@ -3249,10 +3236,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>716964</v>
+        <v>717083</v>
       </c>
       <c r="R27" t="n">
-        <v>6374549</v>
+        <v>6374544</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3312,7 +3299,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128740496</v>
+        <v>128740495</v>
       </c>
       <c r="B28" t="n">
         <v>86927</v>
@@ -3347,10 +3334,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>717083</v>
+        <v>717014</v>
       </c>
       <c r="R28" t="n">
-        <v>6374544</v>
+        <v>6374563</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3410,45 +3397,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128740495</v>
+        <v>128738888</v>
       </c>
       <c r="B29" t="n">
-        <v>86927</v>
+        <v>92756</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6003295</v>
+        <v>1435</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>717014</v>
+        <v>716959</v>
       </c>
       <c r="R29" t="n">
-        <v>6374563</v>
+        <v>6374567</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3478,9 +3468,24 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Luktar mandelkubb.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3496,22 +3501,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128738872</v>
+        <v>128738871</v>
       </c>
       <c r="B30" t="n">
-        <v>91002</v>
+        <v>91003</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3546,7 +3551,7 @@
         <v>716991</v>
       </c>
       <c r="R30" t="n">
-        <v>6374537</v>
+        <v>6374543</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3578,7 +3583,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3588,7 +3593,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128738869</v>
       </c>
       <c r="B2" t="n">
-        <v>86949</v>
+        <v>86976</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128740515</v>
       </c>
       <c r="B3" t="n">
-        <v>92099</v>
+        <v>92126</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128742454</v>
+        <v>128740513</v>
       </c>
       <c r="B4" t="n">
-        <v>90265</v>
+        <v>86780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2072</v>
+        <v>3712</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716979</v>
+        <v>717090</v>
       </c>
       <c r="R4" t="n">
-        <v>6374541</v>
+        <v>6374531</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -947,24 +947,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Artbestämning bekräftad av Michael Krikorev.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,44 +964,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128740513</v>
+        <v>128742454</v>
       </c>
       <c r="B5" t="n">
-        <v>86753</v>
+        <v>90292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3712</v>
+        <v>2072</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717090</v>
+        <v>716979</v>
       </c>
       <c r="R5" t="n">
-        <v>6374531</v>
+        <v>6374541</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1059,9 +1044,24 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Artbestämning bekräftad av Michael Krikorev.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,12 +1076,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1091,7 +1091,7 @@
         <v>128742277</v>
       </c>
       <c r="B6" t="n">
-        <v>57610</v>
+        <v>57637</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>128740493</v>
       </c>
       <c r="B7" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,52 +1289,60 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128738870</v>
+        <v>128740488</v>
       </c>
       <c r="B8" t="n">
-        <v>91003</v>
+        <v>57713</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1357</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716979</v>
+        <v>717042</v>
       </c>
       <c r="R8" t="n">
-        <v>6374541</v>
+        <v>6374557</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,19 +1372,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1391,22 +1389,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128740507</v>
+        <v>128738870</v>
       </c>
       <c r="B9" t="n">
-        <v>86949</v>
+        <v>91030</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1414,21 +1412,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>449</v>
+        <v>1357</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1436,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717045</v>
+        <v>716979</v>
       </c>
       <c r="R9" t="n">
-        <v>6374519</v>
+        <v>6374541</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,9 +1469,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1488,65 +1496,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128740488</v>
+        <v>128740507</v>
       </c>
       <c r="B10" t="n">
-        <v>57686</v>
+        <v>86976</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>449</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717042</v>
+        <v>717045</v>
       </c>
       <c r="R10" t="n">
-        <v>6374557</v>
+        <v>6374519</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1608,7 +1608,7 @@
         <v>128742292</v>
       </c>
       <c r="B11" t="n">
-        <v>86890</v>
+        <v>86917</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>128740492</v>
       </c>
       <c r="B12" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1803,7 +1803,7 @@
         <v>128742260</v>
       </c>
       <c r="B13" t="n">
-        <v>90976</v>
+        <v>91003</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>128740497</v>
       </c>
       <c r="B14" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -1998,7 +1998,7 @@
         <v>128740483</v>
       </c>
       <c r="B15" t="n">
-        <v>86972</v>
+        <v>86999</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2095,7 +2095,7 @@
         <v>128740481</v>
       </c>
       <c r="B16" t="n">
-        <v>86972</v>
+        <v>86999</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2182,17 +2182,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128738874</v>
+        <v>128740479</v>
       </c>
       <c r="B17" t="n">
-        <v>91003</v>
+        <v>86999</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2200,21 +2200,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1357</v>
+        <v>3767</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>716987</v>
+        <v>717060</v>
       </c>
       <c r="R17" t="n">
-        <v>6374546</v>
+        <v>6374568</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2257,71 +2257,62 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128740479</v>
+        <v>128740517</v>
       </c>
       <c r="B18" t="n">
-        <v>86972</v>
+        <v>86917</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2331,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>717060</v>
+        <v>716991</v>
       </c>
       <c r="R18" t="n">
-        <v>6374568</v>
+        <v>6374571</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2375,7 +2366,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2387,39 +2377,39 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128740517</v>
+        <v>128738874</v>
       </c>
       <c r="B19" t="n">
-        <v>86890</v>
+        <v>91030</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3674</v>
+        <v>1357</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2429,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716991</v>
+        <v>716987</v>
       </c>
       <c r="R19" t="n">
-        <v>6374571</v>
+        <v>6374546</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2462,9 +2452,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2479,12 +2479,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2494,7 +2494,7 @@
         <v>128738868</v>
       </c>
       <c r="B20" t="n">
-        <v>86949</v>
+        <v>86976</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>128742265</v>
       </c>
       <c r="B21" t="n">
-        <v>86729</v>
+        <v>86756</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>128740490</v>
       </c>
       <c r="B22" t="n">
-        <v>86729</v>
+        <v>86756</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2795,7 +2795,7 @@
         <v>128738844</v>
       </c>
       <c r="B23" t="n">
-        <v>86972</v>
+        <v>86999</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>128740480</v>
       </c>
       <c r="B24" t="n">
-        <v>86972</v>
+        <v>86999</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -2999,7 +2999,7 @@
         <v>128740494</v>
       </c>
       <c r="B25" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3087,39 +3087,39 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128738872</v>
+        <v>128740496</v>
       </c>
       <c r="B26" t="n">
-        <v>91003</v>
+        <v>86954</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1357</v>
+        <v>6003295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>716991</v>
+        <v>717083</v>
       </c>
       <c r="R26" t="n">
-        <v>6374537</v>
+        <v>6374544</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3162,49 +3162,40 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:03</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:03</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128740496</v>
+        <v>128740495</v>
       </c>
       <c r="B27" t="n">
-        <v>86927</v>
+        <v>86954</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3236,10 +3227,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>717083</v>
+        <v>717014</v>
       </c>
       <c r="R27" t="n">
-        <v>6374544</v>
+        <v>6374563</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3292,39 +3283,39 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128740495</v>
+        <v>128738872</v>
       </c>
       <c r="B28" t="n">
-        <v>86927</v>
+        <v>91030</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6003295</v>
+        <v>1357</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3334,10 +3325,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>717014</v>
+        <v>716991</v>
       </c>
       <c r="R28" t="n">
-        <v>6374563</v>
+        <v>6374537</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3367,30 +3358,39 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3400,7 +3400,7 @@
         <v>128738888</v>
       </c>
       <c r="B29" t="n">
-        <v>92756</v>
+        <v>92783</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>128738871</v>
       </c>
       <c r="B30" t="n">
-        <v>91003</v>
+        <v>91030</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128740513</v>
+        <v>128742454</v>
       </c>
       <c r="B4" t="n">
-        <v>86780</v>
+        <v>90292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3712</v>
+        <v>2072</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717090</v>
+        <v>716979</v>
       </c>
       <c r="R4" t="n">
-        <v>6374531</v>
+        <v>6374541</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -947,9 +947,24 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Artbestämning bekräftad av Michael Krikorev.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -964,44 +979,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128742454</v>
+        <v>128740513</v>
       </c>
       <c r="B5" t="n">
-        <v>90292</v>
+        <v>86780</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2072</v>
+        <v>3712</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716979</v>
+        <v>717090</v>
       </c>
       <c r="R5" t="n">
-        <v>6374541</v>
+        <v>6374531</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1044,24 +1059,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Artbestämning bekräftad av Michael Krikorev.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,22 +1076,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128742277</v>
+        <v>128740493</v>
       </c>
       <c r="B6" t="n">
-        <v>57637</v>
+        <v>86954</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,42 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100001</v>
+        <v>6003295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717082</v>
+        <v>717017</v>
       </c>
       <c r="R6" t="n">
-        <v>6374502</v>
+        <v>6374570</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,39 +1161,35 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Slaktplats av nötskrika.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128740493</v>
+        <v>128742277</v>
       </c>
       <c r="B7" t="n">
-        <v>86954</v>
+        <v>57637</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1209,34 +1197,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6003295</v>
+        <v>100001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717017</v>
+        <v>717082</v>
       </c>
       <c r="R7" t="n">
-        <v>6374570</v>
+        <v>6374502</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,78 +1267,74 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Slaktplats av nötskrika.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128740488</v>
+        <v>128738870</v>
       </c>
       <c r="B8" t="n">
-        <v>57713</v>
+        <v>91030</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1357</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717042</v>
+        <v>716979</v>
       </c>
       <c r="R8" t="n">
-        <v>6374557</v>
+        <v>6374541</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,9 +1364,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,57 +1391,65 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128738870</v>
+        <v>128740488</v>
       </c>
       <c r="B9" t="n">
-        <v>91030</v>
+        <v>57713</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1357</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716979</v>
+        <v>717042</v>
       </c>
       <c r="R9" t="n">
-        <v>6374541</v>
+        <v>6374557</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,19 +1479,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1496,12 +1496,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
+          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2182,17 +2182,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128740479</v>
+        <v>128738874</v>
       </c>
       <c r="B17" t="n">
-        <v>86999</v>
+        <v>91030</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2200,21 +2200,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3767</v>
+        <v>1357</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>717060</v>
+        <v>716987</v>
       </c>
       <c r="R17" t="n">
-        <v>6374568</v>
+        <v>6374546</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2257,62 +2257,71 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128740517</v>
+        <v>128740479</v>
       </c>
       <c r="B18" t="n">
-        <v>86917</v>
+        <v>86999</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2331,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716991</v>
+        <v>717060</v>
       </c>
       <c r="R18" t="n">
-        <v>6374571</v>
+        <v>6374568</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2366,6 +2375,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2377,39 +2387,39 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128738874</v>
+        <v>128740517</v>
       </c>
       <c r="B19" t="n">
-        <v>91030</v>
+        <v>86917</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1357</v>
+        <v>3674</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2419,10 +2429,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716987</v>
+        <v>716991</v>
       </c>
       <c r="R19" t="n">
-        <v>6374546</v>
+        <v>6374571</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2452,19 +2462,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>15:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2479,44 +2479,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128738868</v>
+        <v>128742265</v>
       </c>
       <c r="B20" t="n">
-        <v>86976</v>
+        <v>86756</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>717048</v>
+        <v>717052</v>
       </c>
       <c r="R20" t="n">
-        <v>6374524</v>
+        <v>6374544</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2559,19 +2559,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>15:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2586,19 +2576,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128742265</v>
+        <v>128740490</v>
       </c>
       <c r="B21" t="n">
         <v>86756</v>
@@ -2633,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>717052</v>
+        <v>717075</v>
       </c>
       <c r="R21" t="n">
-        <v>6374544</v>
+        <v>6374568</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2683,44 +2673,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128740490</v>
+        <v>128738868</v>
       </c>
       <c r="B22" t="n">
-        <v>86756</v>
+        <v>86976</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3762</v>
+        <v>449</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2730,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>717075</v>
+        <v>717048</v>
       </c>
       <c r="R22" t="n">
-        <v>6374568</v>
+        <v>6374524</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2763,9 +2753,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2780,12 +2780,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén, Martin Axegård</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Martin Axegård, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128738869</v>
+        <v>128740515</v>
       </c>
       <c r="B2" t="n">
-        <v>86976</v>
+        <v>92131</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>449</v>
+        <v>6031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717060</v>
+        <v>717022</v>
       </c>
       <c r="R2" t="n">
-        <v>6374523</v>
+        <v>6374547</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,19 +743,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,44 +760,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128740515</v>
+        <v>128738869</v>
       </c>
       <c r="B3" t="n">
-        <v>92126</v>
+        <v>86980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6031</v>
+        <v>449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717022</v>
+        <v>717060</v>
       </c>
       <c r="R3" t="n">
-        <v>6374547</v>
+        <v>6374523</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,9 +840,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,44 +867,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128742454</v>
+        <v>128740513</v>
       </c>
       <c r="B4" t="n">
-        <v>90292</v>
+        <v>86784</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2072</v>
+        <v>3712</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716979</v>
+        <v>717090</v>
       </c>
       <c r="R4" t="n">
-        <v>6374541</v>
+        <v>6374531</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -947,24 +947,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Artbestämning bekräftad av Michael Krikorev.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,44 +964,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128740513</v>
+        <v>128742454</v>
       </c>
       <c r="B5" t="n">
-        <v>86780</v>
+        <v>90297</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3712</v>
+        <v>2072</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717090</v>
+        <v>716979</v>
       </c>
       <c r="R5" t="n">
-        <v>6374531</v>
+        <v>6374541</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1059,9 +1044,24 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Artbestämning bekräftad av Michael Krikorev.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,22 +1076,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128740493</v>
+        <v>128742277</v>
       </c>
       <c r="B6" t="n">
-        <v>86954</v>
+        <v>57637</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,34 +1099,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6003295</v>
+        <v>100001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717017</v>
+        <v>717082</v>
       </c>
       <c r="R6" t="n">
-        <v>6374570</v>
+        <v>6374502</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,35 +1169,39 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Slaktplats av nötskrika.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128742277</v>
+        <v>128740493</v>
       </c>
       <c r="B7" t="n">
-        <v>57637</v>
+        <v>86958</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,42 +1209,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100001</v>
+        <v>6003295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717082</v>
+        <v>717017</v>
       </c>
       <c r="R7" t="n">
-        <v>6374502</v>
+        <v>6374570</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,74 +1271,78 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Slaktplats av nötskrika.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128738870</v>
+        <v>128740488</v>
       </c>
       <c r="B8" t="n">
-        <v>91030</v>
+        <v>57713</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1357</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716979</v>
+        <v>717042</v>
       </c>
       <c r="R8" t="n">
-        <v>6374541</v>
+        <v>6374557</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,19 +1372,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1391,65 +1389,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128740488</v>
+        <v>128738870</v>
       </c>
       <c r="B9" t="n">
-        <v>57713</v>
+        <v>91035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1357</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717042</v>
+        <v>716979</v>
       </c>
       <c r="R9" t="n">
-        <v>6374557</v>
+        <v>6374541</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,9 +1469,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1496,12 +1496,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1511,7 +1511,7 @@
         <v>128740507</v>
       </c>
       <c r="B10" t="n">
-        <v>86976</v>
+        <v>86980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>128742292</v>
       </c>
       <c r="B11" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>128740492</v>
       </c>
       <c r="B12" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>128742260</v>
       </c>
       <c r="B13" t="n">
-        <v>91003</v>
+        <v>91008</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>128740497</v>
       </c>
       <c r="B14" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -1998,7 +1998,7 @@
         <v>128740483</v>
       </c>
       <c r="B15" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>128740481</v>
       </c>
       <c r="B16" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,10 +2189,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128738874</v>
+        <v>128740479</v>
       </c>
       <c r="B17" t="n">
-        <v>91030</v>
+        <v>87003</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2200,21 +2200,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1357</v>
+        <v>3767</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>716987</v>
+        <v>717060</v>
       </c>
       <c r="R17" t="n">
-        <v>6374546</v>
+        <v>6374568</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2257,49 +2257,40 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128740479</v>
+        <v>128738874</v>
       </c>
       <c r="B18" t="n">
-        <v>86999</v>
+        <v>91035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2307,21 +2298,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3767</v>
+        <v>1357</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2331,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>717060</v>
+        <v>716987</v>
       </c>
       <c r="R18" t="n">
-        <v>6374568</v>
+        <v>6374546</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2364,30 +2355,39 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2397,7 +2397,7 @@
         <v>128740517</v>
       </c>
       <c r="B19" t="n">
-        <v>86917</v>
+        <v>86921</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>128742265</v>
       </c>
       <c r="B20" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>128740490</v>
       </c>
       <c r="B21" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>128738868</v>
       </c>
       <c r="B22" t="n">
-        <v>86976</v>
+        <v>86980</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>128738844</v>
       </c>
       <c r="B23" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>128740480</v>
       </c>
       <c r="B24" t="n">
-        <v>86999</v>
+        <v>87003</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>128740494</v>
       </c>
       <c r="B25" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3094,32 +3094,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128740496</v>
+        <v>128738872</v>
       </c>
       <c r="B26" t="n">
-        <v>86954</v>
+        <v>91035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6003295</v>
+        <v>1357</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>717083</v>
+        <v>716991</v>
       </c>
       <c r="R26" t="n">
-        <v>6374544</v>
+        <v>6374537</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3162,40 +3162,49 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén, Martin Axegård</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128740495</v>
+        <v>128740496</v>
       </c>
       <c r="B27" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3227,10 +3236,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>717014</v>
+        <v>717083</v>
       </c>
       <c r="R27" t="n">
-        <v>6374563</v>
+        <v>6374544</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3290,32 +3299,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128738872</v>
+        <v>128740495</v>
       </c>
       <c r="B28" t="n">
-        <v>91030</v>
+        <v>86958</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1357</v>
+        <v>6003295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3325,10 +3334,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>716991</v>
+        <v>717014</v>
       </c>
       <c r="R28" t="n">
-        <v>6374537</v>
+        <v>6374563</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3358,39 +3367,30 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>16:03</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>16:03</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3400,7 +3400,7 @@
         <v>128738888</v>
       </c>
       <c r="B29" t="n">
-        <v>92783</v>
+        <v>92788</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>128738871</v>
       </c>
       <c r="B30" t="n">
-        <v>91030</v>
+        <v>91035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128740515</v>
+        <v>128738869</v>
       </c>
       <c r="B2" t="n">
-        <v>92131</v>
+        <v>86981</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6031</v>
+        <v>449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717022</v>
+        <v>717060</v>
       </c>
       <c r="R2" t="n">
-        <v>6374547</v>
+        <v>6374523</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,9 +743,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,44 +770,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128738869</v>
+        <v>128740515</v>
       </c>
       <c r="B3" t="n">
-        <v>86980</v>
+        <v>92136</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>449</v>
+        <v>6031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717060</v>
+        <v>717022</v>
       </c>
       <c r="R3" t="n">
-        <v>6374523</v>
+        <v>6374547</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -840,19 +850,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,44 +867,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128740513</v>
+        <v>128742454</v>
       </c>
       <c r="B4" t="n">
-        <v>86784</v>
+        <v>90302</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3712</v>
+        <v>2072</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717090</v>
+        <v>716979</v>
       </c>
       <c r="R4" t="n">
-        <v>6374531</v>
+        <v>6374541</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -947,9 +947,24 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Artbestämning bekräftad av Michael Krikorev.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -964,44 +979,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128742454</v>
+        <v>128740513</v>
       </c>
       <c r="B5" t="n">
-        <v>90297</v>
+        <v>86784</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2072</v>
+        <v>3712</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716979</v>
+        <v>717090</v>
       </c>
       <c r="R5" t="n">
-        <v>6374541</v>
+        <v>6374531</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1044,24 +1059,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Artbestämning bekräftad av Michael Krikorev.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,22 +1076,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128742277</v>
+        <v>128740493</v>
       </c>
       <c r="B6" t="n">
-        <v>57637</v>
+        <v>86959</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,42 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100001</v>
+        <v>6003295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717082</v>
+        <v>717017</v>
       </c>
       <c r="R6" t="n">
-        <v>6374502</v>
+        <v>6374570</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,39 +1161,35 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Slaktplats av nötskrika.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128740493</v>
+        <v>128742277</v>
       </c>
       <c r="B7" t="n">
-        <v>86958</v>
+        <v>57637</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1209,34 +1197,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6003295</v>
+        <v>100001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717017</v>
+        <v>717082</v>
       </c>
       <c r="R7" t="n">
-        <v>6374570</v>
+        <v>6374502</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,78 +1267,74 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Slaktplats av nötskrika.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128740488</v>
+        <v>128740507</v>
       </c>
       <c r="B8" t="n">
-        <v>57713</v>
+        <v>86981</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717042</v>
+        <v>717045</v>
       </c>
       <c r="R8" t="n">
-        <v>6374557</v>
+        <v>6374519</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,7 +1396,7 @@
         <v>128738870</v>
       </c>
       <c r="B9" t="n">
-        <v>91035</v>
+        <v>91040</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,45 +1500,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128740507</v>
+        <v>128740488</v>
       </c>
       <c r="B10" t="n">
-        <v>86980</v>
+        <v>57713</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>449</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717045</v>
+        <v>717042</v>
       </c>
       <c r="R10" t="n">
-        <v>6374519</v>
+        <v>6374557</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,7 +1608,7 @@
         <v>128742292</v>
       </c>
       <c r="B11" t="n">
-        <v>86921</v>
+        <v>86922</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>128740492</v>
       </c>
       <c r="B12" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>128742260</v>
       </c>
       <c r="B13" t="n">
-        <v>91008</v>
+        <v>91013</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>128740497</v>
       </c>
       <c r="B14" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>128740483</v>
       </c>
       <c r="B15" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>128740481</v>
       </c>
       <c r="B16" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,10 +2189,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128740479</v>
+        <v>128738874</v>
       </c>
       <c r="B17" t="n">
-        <v>87003</v>
+        <v>91040</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2200,21 +2200,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3767</v>
+        <v>1357</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>717060</v>
+        <v>716987</v>
       </c>
       <c r="R17" t="n">
-        <v>6374568</v>
+        <v>6374546</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2257,62 +2257,71 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128738874</v>
+        <v>128740517</v>
       </c>
       <c r="B18" t="n">
-        <v>91035</v>
+        <v>86922</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1357</v>
+        <v>3674</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2331,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716987</v>
+        <v>716991</v>
       </c>
       <c r="R18" t="n">
-        <v>6374546</v>
+        <v>6374571</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2355,19 +2364,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2382,44 +2381,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128740517</v>
+        <v>128740479</v>
       </c>
       <c r="B19" t="n">
-        <v>86921</v>
+        <v>87004</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2429,10 +2428,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716991</v>
+        <v>717060</v>
       </c>
       <c r="R19" t="n">
-        <v>6374571</v>
+        <v>6374568</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2473,6 +2472,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2484,39 +2484,39 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128742265</v>
+        <v>128738868</v>
       </c>
       <c r="B20" t="n">
-        <v>86760</v>
+        <v>86981</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3762</v>
+        <v>449</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>717052</v>
+        <v>717048</v>
       </c>
       <c r="R20" t="n">
-        <v>6374544</v>
+        <v>6374524</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2559,9 +2559,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2576,19 +2586,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128740490</v>
+        <v>128742265</v>
       </c>
       <c r="B21" t="n">
         <v>86760</v>
@@ -2623,10 +2633,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>717075</v>
+        <v>717052</v>
       </c>
       <c r="R21" t="n">
-        <v>6374568</v>
+        <v>6374544</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2673,44 +2683,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128738868</v>
+        <v>128740490</v>
       </c>
       <c r="B22" t="n">
-        <v>86980</v>
+        <v>86760</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2720,10 +2730,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>717048</v>
+        <v>717075</v>
       </c>
       <c r="R22" t="n">
-        <v>6374524</v>
+        <v>6374568</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2753,19 +2763,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>15:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2780,22 +2780,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128738844</v>
+        <v>128740480</v>
       </c>
       <c r="B23" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>717061</v>
+        <v>716999</v>
       </c>
       <c r="R23" t="n">
-        <v>6374502</v>
+        <v>6374513</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2860,19 +2860,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2887,22 +2877,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128740480</v>
+        <v>128738844</v>
       </c>
       <c r="B24" t="n">
-        <v>87003</v>
+        <v>87004</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2934,10 +2924,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>716999</v>
+        <v>717061</v>
       </c>
       <c r="R24" t="n">
-        <v>6374513</v>
+        <v>6374502</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2967,9 +2957,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2984,12 +2984,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -2999,7 +2999,7 @@
         <v>128740494</v>
       </c>
       <c r="B25" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3094,32 +3094,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128738872</v>
+        <v>128740496</v>
       </c>
       <c r="B26" t="n">
-        <v>91035</v>
+        <v>86959</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1357</v>
+        <v>6003295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>716991</v>
+        <v>717083</v>
       </c>
       <c r="R26" t="n">
-        <v>6374537</v>
+        <v>6374544</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3162,49 +3162,40 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:03</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:03</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128740496</v>
+        <v>128740495</v>
       </c>
       <c r="B27" t="n">
-        <v>86958</v>
+        <v>86959</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3236,10 +3227,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>717083</v>
+        <v>717014</v>
       </c>
       <c r="R27" t="n">
-        <v>6374544</v>
+        <v>6374563</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3299,32 +3290,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128740495</v>
+        <v>128738872</v>
       </c>
       <c r="B28" t="n">
-        <v>86958</v>
+        <v>91040</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6003295</v>
+        <v>1357</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3334,10 +3325,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>717014</v>
+        <v>716991</v>
       </c>
       <c r="R28" t="n">
-        <v>6374563</v>
+        <v>6374537</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3367,30 +3358,39 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3400,7 +3400,7 @@
         <v>128738888</v>
       </c>
       <c r="B29" t="n">
-        <v>92788</v>
+        <v>92793</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>128738871</v>
       </c>
       <c r="B30" t="n">
-        <v>91035</v>
+        <v>91040</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128740493</v>
+        <v>128742277</v>
       </c>
       <c r="B6" t="n">
-        <v>86959</v>
+        <v>57637</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,34 +1099,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6003295</v>
+        <v>100001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717017</v>
+        <v>717082</v>
       </c>
       <c r="R6" t="n">
-        <v>6374570</v>
+        <v>6374502</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,35 +1169,39 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Slaktplats av nötskrika.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128742277</v>
+        <v>128740493</v>
       </c>
       <c r="B7" t="n">
-        <v>57637</v>
+        <v>86959</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,42 +1209,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100001</v>
+        <v>6003295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717082</v>
+        <v>717017</v>
       </c>
       <c r="R7" t="n">
-        <v>6374502</v>
+        <v>6374570</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,74 +1271,78 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Slaktplats av nötskrika.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128740507</v>
+        <v>128740488</v>
       </c>
       <c r="B8" t="n">
-        <v>86981</v>
+        <v>57713</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>449</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717045</v>
+        <v>717042</v>
       </c>
       <c r="R8" t="n">
-        <v>6374519</v>
+        <v>6374557</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,10 +1401,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128738870</v>
+        <v>128740507</v>
       </c>
       <c r="B9" t="n">
-        <v>91040</v>
+        <v>86981</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1404,21 +1412,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1357</v>
+        <v>449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1428,10 +1436,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716979</v>
+        <v>717045</v>
       </c>
       <c r="R9" t="n">
-        <v>6374541</v>
+        <v>6374519</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,19 +1469,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1488,65 +1486,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128740488</v>
+        <v>128738870</v>
       </c>
       <c r="B10" t="n">
-        <v>57713</v>
+        <v>91040</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>1357</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717042</v>
+        <v>716979</v>
       </c>
       <c r="R10" t="n">
-        <v>6374557</v>
+        <v>6374541</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,9 +1566,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,12 +1593,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2296,32 +2296,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128740517</v>
+        <v>128740479</v>
       </c>
       <c r="B18" t="n">
-        <v>86922</v>
+        <v>87004</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2331,10 +2331,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716991</v>
+        <v>717060</v>
       </c>
       <c r="R18" t="n">
-        <v>6374571</v>
+        <v>6374568</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2375,6 +2375,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2386,39 +2387,39 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128740479</v>
+        <v>128740517</v>
       </c>
       <c r="B19" t="n">
-        <v>87004</v>
+        <v>86922</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2428,10 +2429,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>717060</v>
+        <v>716991</v>
       </c>
       <c r="R19" t="n">
-        <v>6374568</v>
+        <v>6374571</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2472,7 +2473,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2792,7 +2792,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128740480</v>
+        <v>128738844</v>
       </c>
       <c r="B23" t="n">
         <v>87004</v>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>716999</v>
+        <v>717061</v>
       </c>
       <c r="R23" t="n">
-        <v>6374513</v>
+        <v>6374502</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2860,9 +2860,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2877,19 +2887,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128738844</v>
+        <v>128740480</v>
       </c>
       <c r="B24" t="n">
         <v>87004</v>
@@ -2924,10 +2934,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>717061</v>
+        <v>716999</v>
       </c>
       <c r="R24" t="n">
-        <v>6374502</v>
+        <v>6374513</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2957,19 +2967,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2984,12 +2984,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3094,32 +3094,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128740496</v>
+        <v>128738872</v>
       </c>
       <c r="B26" t="n">
-        <v>86959</v>
+        <v>91040</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6003295</v>
+        <v>1357</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>717083</v>
+        <v>716991</v>
       </c>
       <c r="R26" t="n">
-        <v>6374544</v>
+        <v>6374537</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3162,37 +3162,46 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128740495</v>
+        <v>128740496</v>
       </c>
       <c r="B27" t="n">
         <v>86959</v>
@@ -3227,10 +3236,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>717014</v>
+        <v>717083</v>
       </c>
       <c r="R27" t="n">
-        <v>6374563</v>
+        <v>6374544</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3290,32 +3299,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128738872</v>
+        <v>128740495</v>
       </c>
       <c r="B28" t="n">
-        <v>91040</v>
+        <v>86959</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1357</v>
+        <v>6003295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3325,10 +3334,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>716991</v>
+        <v>717014</v>
       </c>
       <c r="R28" t="n">
-        <v>6374537</v>
+        <v>6374563</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3358,39 +3367,30 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>16:03</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>16:03</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -2296,32 +2296,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128740479</v>
+        <v>128740517</v>
       </c>
       <c r="B18" t="n">
-        <v>87004</v>
+        <v>86922</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2331,10 +2331,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>717060</v>
+        <v>716991</v>
       </c>
       <c r="R18" t="n">
-        <v>6374568</v>
+        <v>6374571</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2375,7 +2375,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2387,39 +2386,39 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128740517</v>
+        <v>128740479</v>
       </c>
       <c r="B19" t="n">
-        <v>86922</v>
+        <v>87004</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2429,10 +2428,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716991</v>
+        <v>717060</v>
       </c>
       <c r="R19" t="n">
-        <v>6374571</v>
+        <v>6374568</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2473,6 +2472,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2484,39 +2484,39 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128738868</v>
+        <v>128742265</v>
       </c>
       <c r="B20" t="n">
-        <v>86981</v>
+        <v>86760</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>717048</v>
+        <v>717052</v>
       </c>
       <c r="R20" t="n">
-        <v>6374524</v>
+        <v>6374544</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2559,19 +2559,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>15:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2586,19 +2576,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128742265</v>
+        <v>128740490</v>
       </c>
       <c r="B21" t="n">
         <v>86760</v>
@@ -2633,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>717052</v>
+        <v>717075</v>
       </c>
       <c r="R21" t="n">
-        <v>6374544</v>
+        <v>6374568</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2683,44 +2673,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128740490</v>
+        <v>128738868</v>
       </c>
       <c r="B22" t="n">
-        <v>86760</v>
+        <v>86981</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3762</v>
+        <v>449</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2730,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>717075</v>
+        <v>717048</v>
       </c>
       <c r="R22" t="n">
-        <v>6374568</v>
+        <v>6374524</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2763,9 +2753,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2780,19 +2780,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128738844</v>
+        <v>128740480</v>
       </c>
       <c r="B23" t="n">
         <v>87004</v>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>717061</v>
+        <v>716999</v>
       </c>
       <c r="R23" t="n">
-        <v>6374502</v>
+        <v>6374513</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2860,19 +2860,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2887,19 +2877,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128740480</v>
+        <v>128738844</v>
       </c>
       <c r="B24" t="n">
         <v>87004</v>
@@ -2934,10 +2924,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>716999</v>
+        <v>717061</v>
       </c>
       <c r="R24" t="n">
-        <v>6374513</v>
+        <v>6374502</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2967,9 +2957,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2984,12 +2984,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128738869</v>
       </c>
       <c r="B2" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128740515</v>
       </c>
       <c r="B3" t="n">
-        <v>92136</v>
+        <v>92140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128742454</v>
       </c>
       <c r="B4" t="n">
-        <v>90302</v>
+        <v>90306</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>128740513</v>
       </c>
       <c r="B5" t="n">
-        <v>86784</v>
+        <v>86788</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>128742277</v>
       </c>
       <c r="B6" t="n">
-        <v>57637</v>
+        <v>57641</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>128740493</v>
       </c>
       <c r="B7" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,53 +1296,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128740488</v>
+        <v>128738870</v>
       </c>
       <c r="B8" t="n">
-        <v>57713</v>
+        <v>91044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1357</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717042</v>
+        <v>716979</v>
       </c>
       <c r="R8" t="n">
-        <v>6374557</v>
+        <v>6374541</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,9 +1364,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,12 +1391,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1404,7 +1406,7 @@
         <v>128740507</v>
       </c>
       <c r="B9" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,45 +1500,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128738870</v>
+        <v>128740488</v>
       </c>
       <c r="B10" t="n">
-        <v>91040</v>
+        <v>57717</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1357</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716979</v>
+        <v>717042</v>
       </c>
       <c r="R10" t="n">
-        <v>6374541</v>
+        <v>6374557</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,19 +1576,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,12 +1593,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1608,7 +1608,7 @@
         <v>128742292</v>
       </c>
       <c r="B11" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>128740492</v>
       </c>
       <c r="B12" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>128742260</v>
       </c>
       <c r="B13" t="n">
-        <v>91013</v>
+        <v>91017</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>128740497</v>
       </c>
       <c r="B14" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>128740483</v>
       </c>
       <c r="B15" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>128740481</v>
       </c>
       <c r="B16" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>128738874</v>
       </c>
       <c r="B17" t="n">
-        <v>91040</v>
+        <v>91044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,32 +2296,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128740517</v>
+        <v>128740479</v>
       </c>
       <c r="B18" t="n">
-        <v>86922</v>
+        <v>87008</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2331,10 +2331,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716991</v>
+        <v>717060</v>
       </c>
       <c r="R18" t="n">
-        <v>6374571</v>
+        <v>6374568</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2375,6 +2375,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2386,39 +2387,39 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128740479</v>
+        <v>128740517</v>
       </c>
       <c r="B19" t="n">
-        <v>87004</v>
+        <v>86926</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2428,10 +2429,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>717060</v>
+        <v>716991</v>
       </c>
       <c r="R19" t="n">
-        <v>6374568</v>
+        <v>6374571</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2472,7 +2473,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2484,39 +2484,39 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128742265</v>
+        <v>128738868</v>
       </c>
       <c r="B20" t="n">
-        <v>86760</v>
+        <v>86985</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3762</v>
+        <v>449</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>717052</v>
+        <v>717048</v>
       </c>
       <c r="R20" t="n">
-        <v>6374544</v>
+        <v>6374524</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2559,9 +2559,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2576,22 +2586,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128740490</v>
+        <v>128742265</v>
       </c>
       <c r="B21" t="n">
-        <v>86760</v>
+        <v>86764</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2623,10 +2633,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>717075</v>
+        <v>717052</v>
       </c>
       <c r="R21" t="n">
-        <v>6374568</v>
+        <v>6374544</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2673,44 +2683,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128738868</v>
+        <v>128740490</v>
       </c>
       <c r="B22" t="n">
-        <v>86981</v>
+        <v>86764</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2720,10 +2730,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>717048</v>
+        <v>717075</v>
       </c>
       <c r="R22" t="n">
-        <v>6374524</v>
+        <v>6374568</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2753,19 +2763,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>15:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2780,22 +2780,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128740480</v>
+        <v>128738844</v>
       </c>
       <c r="B23" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>716999</v>
+        <v>717061</v>
       </c>
       <c r="R23" t="n">
-        <v>6374513</v>
+        <v>6374502</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2860,9 +2860,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2877,22 +2887,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128738844</v>
+        <v>128740480</v>
       </c>
       <c r="B24" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2924,10 +2934,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>717061</v>
+        <v>716999</v>
       </c>
       <c r="R24" t="n">
-        <v>6374502</v>
+        <v>6374513</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2957,19 +2967,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2984,12 +2984,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -2999,7 +2999,7 @@
         <v>128740494</v>
       </c>
       <c r="B25" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>128738872</v>
       </c>
       <c r="B26" t="n">
-        <v>91040</v>
+        <v>91044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>128740496</v>
       </c>
       <c r="B27" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>128740495</v>
       </c>
       <c r="B28" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>128738888</v>
       </c>
       <c r="B29" t="n">
-        <v>92793</v>
+        <v>92797</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>128738871</v>
       </c>
       <c r="B30" t="n">
-        <v>91040</v>
+        <v>91044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128742277</v>
+        <v>128740493</v>
       </c>
       <c r="B6" t="n">
-        <v>57641</v>
+        <v>86963</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,42 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100001</v>
+        <v>6003295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717082</v>
+        <v>717017</v>
       </c>
       <c r="R6" t="n">
-        <v>6374502</v>
+        <v>6374570</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,39 +1161,35 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Slaktplats av nötskrika.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128740493</v>
+        <v>128742277</v>
       </c>
       <c r="B7" t="n">
-        <v>86963</v>
+        <v>57641</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1209,34 +1197,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6003295</v>
+        <v>100001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717017</v>
+        <v>717082</v>
       </c>
       <c r="R7" t="n">
-        <v>6374570</v>
+        <v>6374502</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,25 +1267,29 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Slaktplats av nötskrika.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128738869</v>
+        <v>128740515</v>
       </c>
       <c r="B2" t="n">
-        <v>86985</v>
+        <v>92140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>449</v>
+        <v>6031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717060</v>
+        <v>717022</v>
       </c>
       <c r="R2" t="n">
-        <v>6374523</v>
+        <v>6374547</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,19 +743,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,44 +760,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128740515</v>
+        <v>128738869</v>
       </c>
       <c r="B3" t="n">
-        <v>92140</v>
+        <v>86985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6031</v>
+        <v>449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717022</v>
+        <v>717060</v>
       </c>
       <c r="R3" t="n">
-        <v>6374547</v>
+        <v>6374523</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,9 +840,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,12 +867,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128740493</v>
+        <v>128742277</v>
       </c>
       <c r="B6" t="n">
-        <v>86963</v>
+        <v>57641</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,34 +1099,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6003295</v>
+        <v>100001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717017</v>
+        <v>717082</v>
       </c>
       <c r="R6" t="n">
-        <v>6374570</v>
+        <v>6374502</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,35 +1169,39 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Slaktplats av nötskrika.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128742277</v>
+        <v>128740493</v>
       </c>
       <c r="B7" t="n">
-        <v>57641</v>
+        <v>86963</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,42 +1209,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100001</v>
+        <v>6003295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717082</v>
+        <v>717017</v>
       </c>
       <c r="R7" t="n">
-        <v>6374502</v>
+        <v>6374570</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,39 +1271,35 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Slaktplats av nötskrika.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128738870</v>
+        <v>128740507</v>
       </c>
       <c r="B8" t="n">
-        <v>91044</v>
+        <v>86985</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,21 +1307,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1357</v>
+        <v>449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716979</v>
+        <v>717045</v>
       </c>
       <c r="R8" t="n">
-        <v>6374541</v>
+        <v>6374519</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,19 +1364,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1391,57 +1381,65 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128740507</v>
+        <v>128740488</v>
       </c>
       <c r="B9" t="n">
-        <v>86985</v>
+        <v>57717</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>449</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717045</v>
+        <v>717042</v>
       </c>
       <c r="R9" t="n">
-        <v>6374519</v>
+        <v>6374557</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1493,60 +1491,52 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128740488</v>
+        <v>128738870</v>
       </c>
       <c r="B10" t="n">
-        <v>57717</v>
+        <v>91044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>1357</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717042</v>
+        <v>716979</v>
       </c>
       <c r="R10" t="n">
-        <v>6374557</v>
+        <v>6374541</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,9 +1566,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,12 +1593,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1793,7 +1793,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Martin Axegård, Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128740515</v>
+        <v>128738869</v>
       </c>
       <c r="B2" t="n">
-        <v>92140</v>
+        <v>86990</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6031</v>
+        <v>449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717022</v>
+        <v>717060</v>
       </c>
       <c r="R2" t="n">
-        <v>6374547</v>
+        <v>6374523</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,9 +743,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,44 +770,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128738869</v>
+        <v>128740515</v>
       </c>
       <c r="B3" t="n">
-        <v>86985</v>
+        <v>92145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>449</v>
+        <v>6031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717060</v>
+        <v>717022</v>
       </c>
       <c r="R3" t="n">
-        <v>6374523</v>
+        <v>6374547</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -840,19 +850,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,12 +867,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -882,7 +882,7 @@
         <v>128742454</v>
       </c>
       <c r="B4" t="n">
-        <v>90306</v>
+        <v>90311</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>128740513</v>
       </c>
       <c r="B5" t="n">
-        <v>86788</v>
+        <v>86793</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>128742277</v>
       </c>
       <c r="B6" t="n">
-        <v>57641</v>
+        <v>57644</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>128740493</v>
       </c>
       <c r="B7" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>128740507</v>
       </c>
       <c r="B8" t="n">
-        <v>86985</v>
+        <v>86990</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,53 +1393,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128740488</v>
+        <v>128738870</v>
       </c>
       <c r="B9" t="n">
-        <v>57717</v>
+        <v>91049</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1357</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717042</v>
+        <v>716979</v>
       </c>
       <c r="R9" t="n">
-        <v>6374557</v>
+        <v>6374541</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,9 +1461,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1486,57 +1488,65 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128738870</v>
+        <v>128740488</v>
       </c>
       <c r="B10" t="n">
-        <v>91044</v>
+        <v>57720</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1357</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716979</v>
+        <v>717042</v>
       </c>
       <c r="R10" t="n">
-        <v>6374541</v>
+        <v>6374557</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,19 +1576,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,12 +1593,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1608,7 +1608,7 @@
         <v>128742292</v>
       </c>
       <c r="B11" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>128740492</v>
       </c>
       <c r="B12" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>128742260</v>
       </c>
       <c r="B13" t="n">
-        <v>91017</v>
+        <v>91022</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>128740497</v>
       </c>
       <c r="B14" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>128740483</v>
       </c>
       <c r="B15" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>128740481</v>
       </c>
       <c r="B16" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,10 +2189,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128738874</v>
+        <v>128740479</v>
       </c>
       <c r="B17" t="n">
-        <v>91044</v>
+        <v>87013</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2200,21 +2200,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1357</v>
+        <v>3767</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>716987</v>
+        <v>717060</v>
       </c>
       <c r="R17" t="n">
-        <v>6374546</v>
+        <v>6374568</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2257,49 +2257,40 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128740479</v>
+        <v>128738874</v>
       </c>
       <c r="B18" t="n">
-        <v>87008</v>
+        <v>91049</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2307,21 +2298,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3767</v>
+        <v>1357</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2331,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>717060</v>
+        <v>716987</v>
       </c>
       <c r="R18" t="n">
-        <v>6374568</v>
+        <v>6374546</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2364,30 +2355,39 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2397,7 +2397,7 @@
         <v>128740517</v>
       </c>
       <c r="B19" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>128738868</v>
       </c>
       <c r="B20" t="n">
-        <v>86985</v>
+        <v>86990</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>128742265</v>
       </c>
       <c r="B21" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>128740490</v>
       </c>
       <c r="B22" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>128738844</v>
       </c>
       <c r="B23" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>128740480</v>
       </c>
       <c r="B24" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>128740494</v>
       </c>
       <c r="B25" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3094,32 +3094,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128738872</v>
+        <v>128740496</v>
       </c>
       <c r="B26" t="n">
-        <v>91044</v>
+        <v>86968</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1357</v>
+        <v>6003295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>716991</v>
+        <v>717083</v>
       </c>
       <c r="R26" t="n">
-        <v>6374537</v>
+        <v>6374544</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3162,49 +3162,40 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:03</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:03</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128740496</v>
+        <v>128740495</v>
       </c>
       <c r="B27" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3236,10 +3227,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>717083</v>
+        <v>717014</v>
       </c>
       <c r="R27" t="n">
-        <v>6374544</v>
+        <v>6374563</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3299,32 +3290,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128740495</v>
+        <v>128738872</v>
       </c>
       <c r="B28" t="n">
-        <v>86963</v>
+        <v>91049</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6003295</v>
+        <v>1357</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3334,10 +3325,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>717014</v>
+        <v>716991</v>
       </c>
       <c r="R28" t="n">
-        <v>6374563</v>
+        <v>6374537</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3367,30 +3358,39 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3400,7 +3400,7 @@
         <v>128738888</v>
       </c>
       <c r="B29" t="n">
-        <v>92797</v>
+        <v>92802</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>128738871</v>
       </c>
       <c r="B30" t="n">
-        <v>91044</v>
+        <v>91049</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128740515</v>
+        <v>128738869</v>
       </c>
       <c r="B2" t="n">
-        <v>92153</v>
+        <v>86997</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6031</v>
+        <v>449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717022</v>
+        <v>717060</v>
       </c>
       <c r="R2" t="n">
-        <v>6374547</v>
+        <v>6374523</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,9 +743,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,44 +770,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128738869</v>
+        <v>128740515</v>
       </c>
       <c r="B3" t="n">
-        <v>86997</v>
+        <v>92153</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>449</v>
+        <v>6031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717060</v>
+        <v>717022</v>
       </c>
       <c r="R3" t="n">
-        <v>6374523</v>
+        <v>6374547</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -840,19 +850,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,44 +867,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128740513</v>
+        <v>128742454</v>
       </c>
       <c r="B4" t="n">
-        <v>86800</v>
+        <v>90318</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3712</v>
+        <v>2072</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717090</v>
+        <v>716979</v>
       </c>
       <c r="R4" t="n">
-        <v>6374531</v>
+        <v>6374541</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -947,9 +947,24 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Artbestämning bekräftad av Michael Krikorev.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -964,44 +979,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128742454</v>
+        <v>128740513</v>
       </c>
       <c r="B5" t="n">
-        <v>90318</v>
+        <v>86800</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2072</v>
+        <v>3712</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716979</v>
+        <v>717090</v>
       </c>
       <c r="R5" t="n">
-        <v>6374541</v>
+        <v>6374531</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1044,24 +1059,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Artbestämning bekräftad av Michael Krikorev.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,12 +1076,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128738869</v>
       </c>
       <c r="B2" t="n">
-        <v>86997</v>
+        <v>87000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128740515</v>
       </c>
       <c r="B3" t="n">
-        <v>92153</v>
+        <v>92158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128742454</v>
       </c>
       <c r="B4" t="n">
-        <v>90318</v>
+        <v>90321</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>128740513</v>
       </c>
       <c r="B5" t="n">
-        <v>86800</v>
+        <v>86803</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>128740493</v>
       </c>
       <c r="B6" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>128740507</v>
       </c>
       <c r="B8" t="n">
-        <v>86997</v>
+        <v>87000</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,45 +1393,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128738870</v>
+        <v>128740488</v>
       </c>
       <c r="B9" t="n">
-        <v>91056</v>
+        <v>57720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1357</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716979</v>
+        <v>717042</v>
       </c>
       <c r="R9" t="n">
-        <v>6374541</v>
+        <v>6374557</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,19 +1469,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1488,65 +1486,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128740488</v>
+        <v>128738870</v>
       </c>
       <c r="B10" t="n">
-        <v>57720</v>
+        <v>91059</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>1357</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717042</v>
+        <v>716979</v>
       </c>
       <c r="R10" t="n">
-        <v>6374557</v>
+        <v>6374541</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,9 +1566,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,44 +1593,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128742292</v>
+        <v>128740492</v>
       </c>
       <c r="B11" t="n">
-        <v>86938</v>
+        <v>86978</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>717052</v>
+        <v>717123</v>
       </c>
       <c r="R11" t="n">
-        <v>6374546</v>
+        <v>6374559</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,50 +1684,51 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128740492</v>
+        <v>128742292</v>
       </c>
       <c r="B12" t="n">
-        <v>86975</v>
+        <v>86941</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1737,10 +1738,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>717123</v>
+        <v>717052</v>
       </c>
       <c r="R12" t="n">
-        <v>6374559</v>
+        <v>6374546</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1781,19 +1782,18 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1803,7 +1803,7 @@
         <v>128742260</v>
       </c>
       <c r="B13" t="n">
-        <v>91029</v>
+        <v>91032</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>128740497</v>
       </c>
       <c r="B14" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>128740483</v>
       </c>
       <c r="B15" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>128740481</v>
       </c>
       <c r="B16" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>128738874</v>
       </c>
       <c r="B17" t="n">
-        <v>91056</v>
+        <v>91059</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,32 +2296,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128740479</v>
+        <v>128740517</v>
       </c>
       <c r="B18" t="n">
-        <v>87020</v>
+        <v>86941</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2331,10 +2331,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>717060</v>
+        <v>716991</v>
       </c>
       <c r="R18" t="n">
-        <v>6374568</v>
+        <v>6374571</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2375,7 +2375,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2387,39 +2386,39 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128740517</v>
+        <v>128740479</v>
       </c>
       <c r="B19" t="n">
-        <v>86938</v>
+        <v>87023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2429,10 +2428,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716991</v>
+        <v>717060</v>
       </c>
       <c r="R19" t="n">
-        <v>6374571</v>
+        <v>6374568</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2473,6 +2472,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2494,7 +2494,7 @@
         <v>128738868</v>
       </c>
       <c r="B20" t="n">
-        <v>86997</v>
+        <v>87000</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2598,10 +2598,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128742265</v>
+        <v>128740490</v>
       </c>
       <c r="B21" t="n">
-        <v>86776</v>
+        <v>86779</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>717052</v>
+        <v>717075</v>
       </c>
       <c r="R21" t="n">
-        <v>6374544</v>
+        <v>6374568</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2683,22 +2683,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128740490</v>
+        <v>128742265</v>
       </c>
       <c r="B22" t="n">
-        <v>86776</v>
+        <v>86779</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>717075</v>
+        <v>717052</v>
       </c>
       <c r="R22" t="n">
-        <v>6374568</v>
+        <v>6374544</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2780,12 +2780,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2795,7 +2795,7 @@
         <v>128738844</v>
       </c>
       <c r="B23" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>128740480</v>
       </c>
       <c r="B24" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>128740494</v>
       </c>
       <c r="B25" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>128738872</v>
       </c>
       <c r="B26" t="n">
-        <v>91056</v>
+        <v>91059</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>128740496</v>
       </c>
       <c r="B27" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>128740495</v>
       </c>
       <c r="B28" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>128738888</v>
       </c>
       <c r="B29" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>128738871</v>
       </c>
       <c r="B30" t="n">
-        <v>91056</v>
+        <v>91059</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128738869</v>
       </c>
       <c r="B2" t="n">
-        <v>87000</v>
+        <v>87003</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128740515</v>
       </c>
       <c r="B3" t="n">
-        <v>92158</v>
+        <v>92161</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128742454</v>
       </c>
       <c r="B4" t="n">
-        <v>90321</v>
+        <v>90324</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>128740513</v>
       </c>
       <c r="B5" t="n">
-        <v>86803</v>
+        <v>86806</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128740493</v>
+        <v>128742277</v>
       </c>
       <c r="B6" t="n">
-        <v>86978</v>
+        <v>57644</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,34 +1099,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6003295</v>
+        <v>100001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717017</v>
+        <v>717082</v>
       </c>
       <c r="R6" t="n">
-        <v>6374570</v>
+        <v>6374502</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,35 +1169,39 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Slaktplats av nötskrika.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128742277</v>
+        <v>128740493</v>
       </c>
       <c r="B7" t="n">
-        <v>57644</v>
+        <v>86981</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,42 +1209,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100001</v>
+        <v>6003295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717082</v>
+        <v>717017</v>
       </c>
       <c r="R7" t="n">
-        <v>6374502</v>
+        <v>6374570</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,29 +1271,25 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Slaktplats av nötskrika.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1299,7 +1299,7 @@
         <v>128740507</v>
       </c>
       <c r="B8" t="n">
-        <v>87000</v>
+        <v>87003</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,53 +1393,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128740488</v>
+        <v>128738870</v>
       </c>
       <c r="B9" t="n">
-        <v>57720</v>
+        <v>91062</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1357</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717042</v>
+        <v>716979</v>
       </c>
       <c r="R9" t="n">
-        <v>6374557</v>
+        <v>6374541</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,9 +1461,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1486,57 +1488,65 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128738870</v>
+        <v>128740488</v>
       </c>
       <c r="B10" t="n">
-        <v>91059</v>
+        <v>57720</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1357</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716979</v>
+        <v>717042</v>
       </c>
       <c r="R10" t="n">
-        <v>6374541</v>
+        <v>6374557</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,19 +1576,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,12 +1593,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1608,7 +1608,7 @@
         <v>128740492</v>
       </c>
       <c r="B11" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>128742292</v>
       </c>
       <c r="B12" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>128742260</v>
       </c>
       <c r="B13" t="n">
-        <v>91032</v>
+        <v>91035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>128740497</v>
       </c>
       <c r="B14" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>128740483</v>
       </c>
       <c r="B15" t="n">
-        <v>87023</v>
+        <v>87026</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>128740481</v>
       </c>
       <c r="B16" t="n">
-        <v>87023</v>
+        <v>87026</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,10 +2189,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128738874</v>
+        <v>128740479</v>
       </c>
       <c r="B17" t="n">
-        <v>91059</v>
+        <v>87026</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2200,21 +2200,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1357</v>
+        <v>3767</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>716987</v>
+        <v>717060</v>
       </c>
       <c r="R17" t="n">
-        <v>6374546</v>
+        <v>6374568</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2257,39 +2257,30 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2299,7 +2290,7 @@
         <v>128740517</v>
       </c>
       <c r="B18" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2393,10 +2384,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128740479</v>
+        <v>128738874</v>
       </c>
       <c r="B19" t="n">
-        <v>87023</v>
+        <v>91062</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2404,21 +2395,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3767</v>
+        <v>1357</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2428,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>717060</v>
+        <v>716987</v>
       </c>
       <c r="R19" t="n">
-        <v>6374568</v>
+        <v>6374546</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2461,62 +2452,71 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128738868</v>
+        <v>128742265</v>
       </c>
       <c r="B20" t="n">
-        <v>87000</v>
+        <v>86782</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>717048</v>
+        <v>717052</v>
       </c>
       <c r="R20" t="n">
-        <v>6374524</v>
+        <v>6374544</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2559,19 +2559,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>15:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2586,12 +2576,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2601,7 +2591,7 @@
         <v>128740490</v>
       </c>
       <c r="B21" t="n">
-        <v>86779</v>
+        <v>86782</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2695,32 +2685,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128742265</v>
+        <v>128738868</v>
       </c>
       <c r="B22" t="n">
-        <v>86779</v>
+        <v>87003</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3762</v>
+        <v>449</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2730,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>717052</v>
+        <v>717048</v>
       </c>
       <c r="R22" t="n">
-        <v>6374544</v>
+        <v>6374524</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2763,9 +2753,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2780,12 +2780,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2795,7 +2795,7 @@
         <v>128738844</v>
       </c>
       <c r="B23" t="n">
-        <v>87023</v>
+        <v>87026</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>128740480</v>
       </c>
       <c r="B24" t="n">
-        <v>87023</v>
+        <v>87026</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>128740494</v>
       </c>
       <c r="B25" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>128738872</v>
       </c>
       <c r="B26" t="n">
-        <v>91059</v>
+        <v>91062</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>128740496</v>
       </c>
       <c r="B27" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>128740495</v>
       </c>
       <c r="B28" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>128738888</v>
       </c>
       <c r="B29" t="n">
-        <v>92815</v>
+        <v>92818</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>128738871</v>
       </c>
       <c r="B30" t="n">
-        <v>91059</v>
+        <v>91062</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128738869</v>
+        <v>128740515</v>
       </c>
       <c r="B2" t="n">
-        <v>87003</v>
+        <v>92161</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>449</v>
+        <v>6031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717060</v>
+        <v>717022</v>
       </c>
       <c r="R2" t="n">
-        <v>6374523</v>
+        <v>6374547</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,19 +743,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,44 +760,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128740515</v>
+        <v>128738869</v>
       </c>
       <c r="B3" t="n">
-        <v>92161</v>
+        <v>87003</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6031</v>
+        <v>449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717022</v>
+        <v>717060</v>
       </c>
       <c r="R3" t="n">
-        <v>6374547</v>
+        <v>6374523</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,9 +840,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,12 +867,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128742277</v>
+        <v>128740493</v>
       </c>
       <c r="B6" t="n">
-        <v>57644</v>
+        <v>86981</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,42 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100001</v>
+        <v>6003295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717082</v>
+        <v>717017</v>
       </c>
       <c r="R6" t="n">
-        <v>6374502</v>
+        <v>6374570</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,39 +1161,35 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Slaktplats av nötskrika.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128740493</v>
+        <v>128742277</v>
       </c>
       <c r="B7" t="n">
-        <v>86981</v>
+        <v>57644</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1209,34 +1197,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6003295</v>
+        <v>100001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717017</v>
+        <v>717082</v>
       </c>
       <c r="R7" t="n">
-        <v>6374570</v>
+        <v>6374502</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,25 +1267,29 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Slaktplats av nötskrika.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1605,32 +1605,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128740492</v>
+        <v>128742292</v>
       </c>
       <c r="B11" t="n">
-        <v>86981</v>
+        <v>86944</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>717123</v>
+        <v>717052</v>
       </c>
       <c r="R11" t="n">
-        <v>6374559</v>
+        <v>6374546</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,51 +1684,50 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128742292</v>
+        <v>128740492</v>
       </c>
       <c r="B12" t="n">
-        <v>86944</v>
+        <v>86981</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1738,10 +1737,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>717052</v>
+        <v>717123</v>
       </c>
       <c r="R12" t="n">
-        <v>6374546</v>
+        <v>6374559</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1782,18 +1781,19 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128740493</v>
+        <v>128742277</v>
       </c>
       <c r="B6" t="n">
-        <v>86981</v>
+        <v>57644</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,34 +1099,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6003295</v>
+        <v>100001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717017</v>
+        <v>717082</v>
       </c>
       <c r="R6" t="n">
-        <v>6374570</v>
+        <v>6374502</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,35 +1169,39 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Slaktplats av nötskrika.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128742277</v>
+        <v>128740493</v>
       </c>
       <c r="B7" t="n">
-        <v>57644</v>
+        <v>86981</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,42 +1209,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100001</v>
+        <v>6003295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717082</v>
+        <v>717017</v>
       </c>
       <c r="R7" t="n">
-        <v>6374502</v>
+        <v>6374570</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,39 +1271,35 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Slaktplats av nötskrika.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128740507</v>
+        <v>128738870</v>
       </c>
       <c r="B8" t="n">
-        <v>87003</v>
+        <v>91062</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,21 +1307,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>449</v>
+        <v>1357</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717045</v>
+        <v>716979</v>
       </c>
       <c r="R8" t="n">
-        <v>6374519</v>
+        <v>6374541</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,9 +1364,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1381,22 +1391,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128738870</v>
+        <v>128740507</v>
       </c>
       <c r="B9" t="n">
-        <v>91062</v>
+        <v>87003</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1404,21 +1414,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1357</v>
+        <v>449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1428,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716979</v>
+        <v>717045</v>
       </c>
       <c r="R9" t="n">
-        <v>6374541</v>
+        <v>6374519</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,19 +1471,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1488,12 +1488,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1605,32 +1605,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128742292</v>
+        <v>128740492</v>
       </c>
       <c r="B11" t="n">
-        <v>86944</v>
+        <v>86981</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>717052</v>
+        <v>717123</v>
       </c>
       <c r="R11" t="n">
-        <v>6374546</v>
+        <v>6374559</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,50 +1684,51 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128740492</v>
+        <v>128742292</v>
       </c>
       <c r="B12" t="n">
-        <v>86981</v>
+        <v>86944</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1737,10 +1738,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>717123</v>
+        <v>717052</v>
       </c>
       <c r="R12" t="n">
-        <v>6374559</v>
+        <v>6374546</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1781,19 +1782,18 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2189,10 +2189,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128740479</v>
+        <v>128738874</v>
       </c>
       <c r="B17" t="n">
-        <v>87026</v>
+        <v>91062</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2200,21 +2200,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3767</v>
+        <v>1357</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>717060</v>
+        <v>716987</v>
       </c>
       <c r="R17" t="n">
-        <v>6374568</v>
+        <v>6374546</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2257,62 +2257,71 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128740517</v>
+        <v>128740479</v>
       </c>
       <c r="B18" t="n">
-        <v>86944</v>
+        <v>87026</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2331,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716991</v>
+        <v>717060</v>
       </c>
       <c r="R18" t="n">
-        <v>6374571</v>
+        <v>6374568</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2366,6 +2375,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2377,39 +2387,39 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128738874</v>
+        <v>128740517</v>
       </c>
       <c r="B19" t="n">
-        <v>91062</v>
+        <v>86944</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1357</v>
+        <v>3674</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2419,10 +2429,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716987</v>
+        <v>716991</v>
       </c>
       <c r="R19" t="n">
-        <v>6374546</v>
+        <v>6374571</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2452,19 +2462,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>15:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2479,44 +2479,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128742265</v>
+        <v>128738868</v>
       </c>
       <c r="B20" t="n">
-        <v>86782</v>
+        <v>87003</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3762</v>
+        <v>449</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>717052</v>
+        <v>717048</v>
       </c>
       <c r="R20" t="n">
-        <v>6374544</v>
+        <v>6374524</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2559,9 +2559,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2576,19 +2586,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128740490</v>
+        <v>128742265</v>
       </c>
       <c r="B21" t="n">
         <v>86782</v>
@@ -2623,10 +2633,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>717075</v>
+        <v>717052</v>
       </c>
       <c r="R21" t="n">
-        <v>6374568</v>
+        <v>6374544</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2673,44 +2683,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128738868</v>
+        <v>128740490</v>
       </c>
       <c r="B22" t="n">
-        <v>87003</v>
+        <v>86782</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2720,10 +2730,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>717048</v>
+        <v>717075</v>
       </c>
       <c r="R22" t="n">
-        <v>6374524</v>
+        <v>6374568</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2753,19 +2763,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>15:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2780,12 +2780,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128742454</v>
+        <v>128740513</v>
       </c>
       <c r="B4" t="n">
-        <v>90324</v>
+        <v>86806</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2072</v>
+        <v>3712</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716979</v>
+        <v>717090</v>
       </c>
       <c r="R4" t="n">
-        <v>6374541</v>
+        <v>6374531</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -947,24 +947,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Artbestämning bekräftad av Michael Krikorev.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,44 +964,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128740513</v>
+        <v>128742454</v>
       </c>
       <c r="B5" t="n">
-        <v>86806</v>
+        <v>90324</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3712</v>
+        <v>2072</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717090</v>
+        <v>716979</v>
       </c>
       <c r="R5" t="n">
-        <v>6374531</v>
+        <v>6374541</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1059,9 +1044,24 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Artbestämning bekräftad av Michael Krikorev.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,22 +1076,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128742277</v>
+        <v>128740493</v>
       </c>
       <c r="B6" t="n">
-        <v>57644</v>
+        <v>86981</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,42 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100001</v>
+        <v>6003295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717082</v>
+        <v>717017</v>
       </c>
       <c r="R6" t="n">
-        <v>6374502</v>
+        <v>6374570</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,39 +1161,35 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Slaktplats av nötskrika.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128740493</v>
+        <v>128742277</v>
       </c>
       <c r="B7" t="n">
-        <v>86981</v>
+        <v>57644</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1209,34 +1197,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6003295</v>
+        <v>100001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717017</v>
+        <v>717082</v>
       </c>
       <c r="R7" t="n">
-        <v>6374570</v>
+        <v>6374502</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,35 +1267,39 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Slaktplats av nötskrika.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128738870</v>
+        <v>128740507</v>
       </c>
       <c r="B8" t="n">
-        <v>91062</v>
+        <v>87003</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,21 +1307,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1357</v>
+        <v>449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716979</v>
+        <v>717045</v>
       </c>
       <c r="R8" t="n">
-        <v>6374541</v>
+        <v>6374519</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,19 +1364,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1391,22 +1381,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128740507</v>
+        <v>128738870</v>
       </c>
       <c r="B9" t="n">
-        <v>87003</v>
+        <v>91062</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1414,21 +1404,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>449</v>
+        <v>1357</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717045</v>
+        <v>716979</v>
       </c>
       <c r="R9" t="n">
-        <v>6374519</v>
+        <v>6374541</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,9 +1461,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1488,12 +1488,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1605,32 +1605,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128740492</v>
+        <v>128742292</v>
       </c>
       <c r="B11" t="n">
-        <v>86981</v>
+        <v>86944</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>717123</v>
+        <v>717052</v>
       </c>
       <c r="R11" t="n">
-        <v>6374559</v>
+        <v>6374546</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,51 +1684,50 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128742292</v>
+        <v>128740492</v>
       </c>
       <c r="B12" t="n">
-        <v>86944</v>
+        <v>86981</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1738,10 +1737,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>717052</v>
+        <v>717123</v>
       </c>
       <c r="R12" t="n">
-        <v>6374546</v>
+        <v>6374559</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1782,18 +1781,19 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2189,10 +2189,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128738874</v>
+        <v>128740479</v>
       </c>
       <c r="B17" t="n">
-        <v>91062</v>
+        <v>87026</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2200,21 +2200,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1357</v>
+        <v>3767</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>716987</v>
+        <v>717060</v>
       </c>
       <c r="R17" t="n">
-        <v>6374546</v>
+        <v>6374568</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2257,49 +2257,40 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128740479</v>
+        <v>128738874</v>
       </c>
       <c r="B18" t="n">
-        <v>87026</v>
+        <v>91062</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2307,21 +2298,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3767</v>
+        <v>1357</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2331,10 +2322,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>717060</v>
+        <v>716987</v>
       </c>
       <c r="R18" t="n">
-        <v>6374568</v>
+        <v>6374546</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2364,30 +2355,39 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2491,32 +2491,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128738868</v>
+        <v>128742265</v>
       </c>
       <c r="B20" t="n">
-        <v>87003</v>
+        <v>86782</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>717048</v>
+        <v>717052</v>
       </c>
       <c r="R20" t="n">
-        <v>6374524</v>
+        <v>6374544</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2559,19 +2559,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>15:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2586,19 +2576,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128742265</v>
+        <v>128740490</v>
       </c>
       <c r="B21" t="n">
         <v>86782</v>
@@ -2633,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>717052</v>
+        <v>717075</v>
       </c>
       <c r="R21" t="n">
-        <v>6374544</v>
+        <v>6374568</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2683,44 +2673,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128740490</v>
+        <v>128738868</v>
       </c>
       <c r="B22" t="n">
-        <v>86782</v>
+        <v>87003</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3762</v>
+        <v>449</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2730,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>717075</v>
+        <v>717048</v>
       </c>
       <c r="R22" t="n">
-        <v>6374568</v>
+        <v>6374524</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2763,9 +2753,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2780,12 +2780,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128740515</v>
+        <v>128738869</v>
       </c>
       <c r="B2" t="n">
-        <v>92161</v>
+        <v>87007</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6031</v>
+        <v>449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717022</v>
+        <v>717060</v>
       </c>
       <c r="R2" t="n">
-        <v>6374547</v>
+        <v>6374523</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,9 +743,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,44 +770,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128738869</v>
+        <v>128740515</v>
       </c>
       <c r="B3" t="n">
-        <v>87003</v>
+        <v>92168</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>449</v>
+        <v>6031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717060</v>
+        <v>717022</v>
       </c>
       <c r="R3" t="n">
-        <v>6374523</v>
+        <v>6374547</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -840,19 +850,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,12 +867,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -882,7 +882,7 @@
         <v>128740513</v>
       </c>
       <c r="B4" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>128742454</v>
       </c>
       <c r="B5" t="n">
-        <v>90324</v>
+        <v>90328</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128740493</v>
+        <v>128742277</v>
       </c>
       <c r="B6" t="n">
-        <v>86981</v>
+        <v>57646</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,34 +1099,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6003295</v>
+        <v>100001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717017</v>
+        <v>717082</v>
       </c>
       <c r="R6" t="n">
-        <v>6374570</v>
+        <v>6374502</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,35 +1169,39 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Slaktplats av nötskrika.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128742277</v>
+        <v>128740493</v>
       </c>
       <c r="B7" t="n">
-        <v>57644</v>
+        <v>86985</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1197,42 +1209,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100001</v>
+        <v>6003295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717082</v>
+        <v>717017</v>
       </c>
       <c r="R7" t="n">
-        <v>6374502</v>
+        <v>6374570</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,29 +1271,25 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Slaktplats av nötskrika.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1299,7 +1299,7 @@
         <v>128740507</v>
       </c>
       <c r="B8" t="n">
-        <v>87003</v>
+        <v>87007</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>128738870</v>
       </c>
       <c r="B9" t="n">
-        <v>91062</v>
+        <v>91066</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>128740488</v>
       </c>
       <c r="B10" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1605,32 +1605,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128742292</v>
+        <v>128740492</v>
       </c>
       <c r="B11" t="n">
-        <v>86944</v>
+        <v>86985</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>717052</v>
+        <v>717123</v>
       </c>
       <c r="R11" t="n">
-        <v>6374546</v>
+        <v>6374559</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,50 +1684,51 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128740492</v>
+        <v>128742292</v>
       </c>
       <c r="B12" t="n">
-        <v>86981</v>
+        <v>86948</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1737,10 +1738,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>717123</v>
+        <v>717052</v>
       </c>
       <c r="R12" t="n">
-        <v>6374559</v>
+        <v>6374546</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1781,19 +1782,18 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1803,7 +1803,7 @@
         <v>128742260</v>
       </c>
       <c r="B13" t="n">
-        <v>91035</v>
+        <v>91039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>128740497</v>
       </c>
       <c r="B14" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>128740483</v>
       </c>
       <c r="B15" t="n">
-        <v>87026</v>
+        <v>87030</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>128740481</v>
       </c>
       <c r="B16" t="n">
-        <v>87026</v>
+        <v>87030</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2189,10 +2189,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128740479</v>
+        <v>128738874</v>
       </c>
       <c r="B17" t="n">
-        <v>87026</v>
+        <v>91066</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2200,21 +2200,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3767</v>
+        <v>1357</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>717060</v>
+        <v>716987</v>
       </c>
       <c r="R17" t="n">
-        <v>6374568</v>
+        <v>6374546</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2257,40 +2257,49 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128738874</v>
+        <v>128740479</v>
       </c>
       <c r="B18" t="n">
-        <v>91062</v>
+        <v>87030</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2298,21 +2307,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1357</v>
+        <v>3767</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2331,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716987</v>
+        <v>717060</v>
       </c>
       <c r="R18" t="n">
-        <v>6374546</v>
+        <v>6374568</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2355,39 +2364,30 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2397,7 +2397,7 @@
         <v>128740517</v>
       </c>
       <c r="B19" t="n">
-        <v>86944</v>
+        <v>86948</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>128742265</v>
       </c>
       <c r="B20" t="n">
-        <v>86782</v>
+        <v>86786</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>128740490</v>
       </c>
       <c r="B21" t="n">
-        <v>86782</v>
+        <v>86786</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>128738868</v>
       </c>
       <c r="B22" t="n">
-        <v>87003</v>
+        <v>87007</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>128738844</v>
       </c>
       <c r="B23" t="n">
-        <v>87026</v>
+        <v>87030</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>128740480</v>
       </c>
       <c r="B24" t="n">
-        <v>87026</v>
+        <v>87030</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>128740494</v>
       </c>
       <c r="B25" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>128738872</v>
       </c>
       <c r="B26" t="n">
-        <v>91062</v>
+        <v>91066</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>128740496</v>
       </c>
       <c r="B27" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>128740495</v>
       </c>
       <c r="B28" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>128738888</v>
       </c>
       <c r="B29" t="n">
-        <v>92818</v>
+        <v>92825</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>128738871</v>
       </c>
       <c r="B30" t="n">
-        <v>91062</v>
+        <v>91066</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -1296,45 +1296,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128740507</v>
+        <v>128740488</v>
       </c>
       <c r="B8" t="n">
-        <v>87007</v>
+        <v>57722</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>449</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717045</v>
+        <v>717042</v>
       </c>
       <c r="R8" t="n">
-        <v>6374519</v>
+        <v>6374557</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,10 +1401,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128738870</v>
+        <v>128740507</v>
       </c>
       <c r="B9" t="n">
-        <v>91066</v>
+        <v>87007</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1404,21 +1412,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1357</v>
+        <v>449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1428,10 +1436,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716979</v>
+        <v>717045</v>
       </c>
       <c r="R9" t="n">
-        <v>6374541</v>
+        <v>6374519</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,19 +1469,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1488,65 +1486,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128740488</v>
+        <v>128738870</v>
       </c>
       <c r="B10" t="n">
-        <v>57722</v>
+        <v>91066</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>1357</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717042</v>
+        <v>716979</v>
       </c>
       <c r="R10" t="n">
-        <v>6374557</v>
+        <v>6374541</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,9 +1566,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,44 +1593,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128740492</v>
+        <v>128742292</v>
       </c>
       <c r="B11" t="n">
-        <v>86985</v>
+        <v>86948</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>717123</v>
+        <v>717052</v>
       </c>
       <c r="R11" t="n">
-        <v>6374559</v>
+        <v>6374546</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,51 +1684,50 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128742292</v>
+        <v>128740492</v>
       </c>
       <c r="B12" t="n">
-        <v>86948</v>
+        <v>86985</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1738,10 +1737,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>717052</v>
+        <v>717123</v>
       </c>
       <c r="R12" t="n">
-        <v>6374546</v>
+        <v>6374559</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1782,18 +1781,19 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2491,32 +2491,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128742265</v>
+        <v>128738868</v>
       </c>
       <c r="B20" t="n">
-        <v>86786</v>
+        <v>87007</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3762</v>
+        <v>449</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>717052</v>
+        <v>717048</v>
       </c>
       <c r="R20" t="n">
-        <v>6374544</v>
+        <v>6374524</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2559,9 +2559,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2576,19 +2586,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128740490</v>
+        <v>128742265</v>
       </c>
       <c r="B21" t="n">
         <v>86786</v>
@@ -2623,10 +2633,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>717075</v>
+        <v>717052</v>
       </c>
       <c r="R21" t="n">
-        <v>6374568</v>
+        <v>6374544</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2673,44 +2683,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128738868</v>
+        <v>128740490</v>
       </c>
       <c r="B22" t="n">
-        <v>87007</v>
+        <v>86786</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2720,10 +2730,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>717048</v>
+        <v>717075</v>
       </c>
       <c r="R22" t="n">
-        <v>6374524</v>
+        <v>6374568</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2753,19 +2763,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>15:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2780,12 +2780,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -1296,53 +1296,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128740488</v>
+        <v>128740507</v>
       </c>
       <c r="B8" t="n">
-        <v>57722</v>
+        <v>87007</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717042</v>
+        <v>717045</v>
       </c>
       <c r="R8" t="n">
-        <v>6374557</v>
+        <v>6374519</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1401,10 +1393,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128740507</v>
+        <v>128738870</v>
       </c>
       <c r="B9" t="n">
-        <v>87007</v>
+        <v>91066</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1412,21 +1404,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>449</v>
+        <v>1357</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1436,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717045</v>
+        <v>716979</v>
       </c>
       <c r="R9" t="n">
-        <v>6374519</v>
+        <v>6374541</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,9 +1461,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1486,57 +1488,65 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128738870</v>
+        <v>128740488</v>
       </c>
       <c r="B10" t="n">
-        <v>91066</v>
+        <v>57722</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1357</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716979</v>
+        <v>717042</v>
       </c>
       <c r="R10" t="n">
-        <v>6374541</v>
+        <v>6374557</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,19 +1576,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,44 +1593,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128742292</v>
+        <v>128740492</v>
       </c>
       <c r="B11" t="n">
-        <v>86948</v>
+        <v>86985</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3674</v>
+        <v>6003295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>717052</v>
+        <v>717123</v>
       </c>
       <c r="R11" t="n">
-        <v>6374546</v>
+        <v>6374559</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,50 +1684,51 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128740492</v>
+        <v>128742292</v>
       </c>
       <c r="B12" t="n">
-        <v>86985</v>
+        <v>86948</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1737,10 +1738,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>717123</v>
+        <v>717052</v>
       </c>
       <c r="R12" t="n">
-        <v>6374559</v>
+        <v>6374546</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1781,19 +1782,18 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -3094,32 +3094,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128738872</v>
+        <v>128740496</v>
       </c>
       <c r="B26" t="n">
-        <v>91066</v>
+        <v>86985</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1357</v>
+        <v>6003295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>716991</v>
+        <v>717083</v>
       </c>
       <c r="R26" t="n">
-        <v>6374537</v>
+        <v>6374544</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3162,46 +3162,37 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:03</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:03</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128740496</v>
+        <v>128740495</v>
       </c>
       <c r="B27" t="n">
         <v>86985</v>
@@ -3236,10 +3227,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>717083</v>
+        <v>717014</v>
       </c>
       <c r="R27" t="n">
-        <v>6374544</v>
+        <v>6374563</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3299,32 +3290,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128740495</v>
+        <v>128738872</v>
       </c>
       <c r="B28" t="n">
-        <v>86985</v>
+        <v>91066</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6003295</v>
+        <v>1357</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3334,10 +3325,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>717014</v>
+        <v>716991</v>
       </c>
       <c r="R28" t="n">
-        <v>6374563</v>
+        <v>6374537</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3367,30 +3358,39 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3400,7 +3400,7 @@
         <v>128738888</v>
       </c>
       <c r="B29" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>128738871</v>
       </c>
       <c r="B30" t="n">
-        <v>91066</v>
+        <v>91073</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128738869</v>
       </c>
       <c r="B2" t="n">
-        <v>87007</v>
+        <v>87016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128740515</v>
       </c>
       <c r="B3" t="n">
-        <v>92168</v>
+        <v>92177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128740513</v>
+        <v>128742454</v>
       </c>
       <c r="B4" t="n">
-        <v>86810</v>
+        <v>90337</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3712</v>
+        <v>2072</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717090</v>
+        <v>716979</v>
       </c>
       <c r="R4" t="n">
-        <v>6374531</v>
+        <v>6374541</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -947,9 +947,24 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Artbestämning bekräftad av Michael Krikorev.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -964,44 +979,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128742454</v>
+        <v>128740513</v>
       </c>
       <c r="B5" t="n">
-        <v>90328</v>
+        <v>86819</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2072</v>
+        <v>3712</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716979</v>
+        <v>717090</v>
       </c>
       <c r="R5" t="n">
-        <v>6374541</v>
+        <v>6374531</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1044,24 +1059,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Artbestämning bekräftad av Michael Krikorev.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,12 +1076,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1091,7 +1091,7 @@
         <v>128742277</v>
       </c>
       <c r="B6" t="n">
-        <v>57646</v>
+        <v>57648</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>128740493</v>
       </c>
       <c r="B7" t="n">
-        <v>86985</v>
+        <v>86994</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128740507</v>
+        <v>128738870</v>
       </c>
       <c r="B8" t="n">
-        <v>87007</v>
+        <v>91075</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,21 +1307,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>449</v>
+        <v>1357</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717045</v>
+        <v>716979</v>
       </c>
       <c r="R8" t="n">
-        <v>6374519</v>
+        <v>6374541</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,9 +1364,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1381,22 +1391,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128738870</v>
+        <v>128740507</v>
       </c>
       <c r="B9" t="n">
-        <v>91066</v>
+        <v>87016</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1404,21 +1414,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1357</v>
+        <v>449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1428,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716979</v>
+        <v>717045</v>
       </c>
       <c r="R9" t="n">
-        <v>6374541</v>
+        <v>6374519</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,19 +1471,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1488,12 +1488,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1503,7 +1503,7 @@
         <v>128740488</v>
       </c>
       <c r="B10" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>128740492</v>
       </c>
       <c r="B11" t="n">
-        <v>86985</v>
+        <v>86994</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>128742292</v>
       </c>
       <c r="B12" t="n">
-        <v>86948</v>
+        <v>86957</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>128742260</v>
       </c>
       <c r="B13" t="n">
-        <v>91039</v>
+        <v>91048</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>128740497</v>
       </c>
       <c r="B14" t="n">
-        <v>86985</v>
+        <v>86994</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>128740483</v>
       </c>
       <c r="B15" t="n">
-        <v>87030</v>
+        <v>87039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>128740481</v>
       </c>
       <c r="B16" t="n">
-        <v>87030</v>
+        <v>87039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>128738874</v>
       </c>
       <c r="B17" t="n">
-        <v>91066</v>
+        <v>91075</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,32 +2296,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128740479</v>
+        <v>128740517</v>
       </c>
       <c r="B18" t="n">
-        <v>87030</v>
+        <v>86957</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2331,10 +2331,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>717060</v>
+        <v>716991</v>
       </c>
       <c r="R18" t="n">
-        <v>6374568</v>
+        <v>6374571</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2375,7 +2375,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2387,39 +2386,39 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128740517</v>
+        <v>128740479</v>
       </c>
       <c r="B19" t="n">
-        <v>86948</v>
+        <v>87039</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2429,10 +2428,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716991</v>
+        <v>717060</v>
       </c>
       <c r="R19" t="n">
-        <v>6374571</v>
+        <v>6374568</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2473,6 +2472,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2484,39 +2484,39 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128738868</v>
+        <v>128742265</v>
       </c>
       <c r="B20" t="n">
-        <v>87007</v>
+        <v>86795</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>449</v>
+        <v>3762</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>717048</v>
+        <v>717052</v>
       </c>
       <c r="R20" t="n">
-        <v>6374524</v>
+        <v>6374544</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2559,19 +2559,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>15:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2586,22 +2576,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128742265</v>
+        <v>128740490</v>
       </c>
       <c r="B21" t="n">
-        <v>86786</v>
+        <v>86795</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2633,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>717052</v>
+        <v>717075</v>
       </c>
       <c r="R21" t="n">
-        <v>6374544</v>
+        <v>6374568</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2683,44 +2673,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128740490</v>
+        <v>128738868</v>
       </c>
       <c r="B22" t="n">
-        <v>86786</v>
+        <v>87016</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3762</v>
+        <v>449</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2730,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>717075</v>
+        <v>717048</v>
       </c>
       <c r="R22" t="n">
-        <v>6374568</v>
+        <v>6374524</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2763,9 +2753,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2780,12 +2780,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2795,7 +2795,7 @@
         <v>128738844</v>
       </c>
       <c r="B23" t="n">
-        <v>87030</v>
+        <v>87039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>128740480</v>
       </c>
       <c r="B24" t="n">
-        <v>87030</v>
+        <v>87039</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>128740494</v>
       </c>
       <c r="B25" t="n">
-        <v>86985</v>
+        <v>86994</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3094,32 +3094,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128740496</v>
+        <v>128738872</v>
       </c>
       <c r="B26" t="n">
-        <v>86985</v>
+        <v>91075</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6003295</v>
+        <v>1357</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>717083</v>
+        <v>716991</v>
       </c>
       <c r="R26" t="n">
-        <v>6374544</v>
+        <v>6374537</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3162,40 +3162,49 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128740495</v>
+        <v>128740496</v>
       </c>
       <c r="B27" t="n">
-        <v>86985</v>
+        <v>86994</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3227,10 +3236,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>717014</v>
+        <v>717083</v>
       </c>
       <c r="R27" t="n">
-        <v>6374563</v>
+        <v>6374544</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3290,32 +3299,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128738872</v>
+        <v>128740495</v>
       </c>
       <c r="B28" t="n">
-        <v>91066</v>
+        <v>86994</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1357</v>
+        <v>6003295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3325,10 +3334,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>716991</v>
+        <v>717014</v>
       </c>
       <c r="R28" t="n">
-        <v>6374537</v>
+        <v>6374563</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3358,39 +3367,30 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>16:03</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>16:03</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3400,7 +3400,7 @@
         <v>128738888</v>
       </c>
       <c r="B29" t="n">
-        <v>92832</v>
+        <v>92834</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>128738871</v>
       </c>
       <c r="B30" t="n">
-        <v>91073</v>
+        <v>91075</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128738869</v>
+        <v>128740515</v>
       </c>
       <c r="B2" t="n">
-        <v>87016</v>
+        <v>92177</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>449</v>
+        <v>6031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717060</v>
+        <v>717022</v>
       </c>
       <c r="R2" t="n">
-        <v>6374523</v>
+        <v>6374547</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,19 +743,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,44 +760,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128740515</v>
+        <v>128738869</v>
       </c>
       <c r="B3" t="n">
-        <v>92177</v>
+        <v>87016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6031</v>
+        <v>449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717022</v>
+        <v>717060</v>
       </c>
       <c r="R3" t="n">
-        <v>6374547</v>
+        <v>6374523</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,9 +840,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,44 +867,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128742454</v>
+        <v>128740513</v>
       </c>
       <c r="B4" t="n">
-        <v>90337</v>
+        <v>86819</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2072</v>
+        <v>3712</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716979</v>
+        <v>717090</v>
       </c>
       <c r="R4" t="n">
-        <v>6374541</v>
+        <v>6374531</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -947,24 +947,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Artbestämning bekräftad av Michael Krikorev.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,44 +964,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128740513</v>
+        <v>128742454</v>
       </c>
       <c r="B5" t="n">
-        <v>86819</v>
+        <v>90337</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3712</v>
+        <v>2072</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>717090</v>
+        <v>716979</v>
       </c>
       <c r="R5" t="n">
-        <v>6374531</v>
+        <v>6374541</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1059,9 +1044,24 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Artbestämning bekräftad av Michael Krikorev.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,22 +1076,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128742277</v>
+        <v>128740493</v>
       </c>
       <c r="B6" t="n">
-        <v>57648</v>
+        <v>86994</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,42 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100001</v>
+        <v>6003295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717082</v>
+        <v>717017</v>
       </c>
       <c r="R6" t="n">
-        <v>6374502</v>
+        <v>6374570</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,39 +1161,35 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Slaktplats av nötskrika.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128740493</v>
+        <v>128742277</v>
       </c>
       <c r="B7" t="n">
-        <v>86994</v>
+        <v>57648</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1209,34 +1197,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6003295</v>
+        <v>100001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717017</v>
+        <v>717082</v>
       </c>
       <c r="R7" t="n">
-        <v>6374570</v>
+        <v>6374502</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,70 +1267,82 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Slaktplats av nötskrika.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128738870</v>
+        <v>128740488</v>
       </c>
       <c r="B8" t="n">
-        <v>91075</v>
+        <v>57724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1357</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716979</v>
+        <v>717042</v>
       </c>
       <c r="R8" t="n">
-        <v>6374541</v>
+        <v>6374557</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,19 +1372,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:27</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1391,12 +1389,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1500,53 +1498,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128740488</v>
+        <v>128738870</v>
       </c>
       <c r="B10" t="n">
-        <v>57724</v>
+        <v>91075</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>1357</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717042</v>
+        <v>716979</v>
       </c>
       <c r="R10" t="n">
-        <v>6374557</v>
+        <v>6374541</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,9 +1566,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,12 +1593,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2189,10 +2189,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128738874</v>
+        <v>128740479</v>
       </c>
       <c r="B17" t="n">
-        <v>91075</v>
+        <v>87039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2200,21 +2200,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1357</v>
+        <v>3767</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>716987</v>
+        <v>717060</v>
       </c>
       <c r="R17" t="n">
-        <v>6374546</v>
+        <v>6374568</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2257,39 +2257,30 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2393,10 +2384,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128740479</v>
+        <v>128738874</v>
       </c>
       <c r="B19" t="n">
-        <v>87039</v>
+        <v>91075</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2404,21 +2395,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3767</v>
+        <v>1357</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2428,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>717060</v>
+        <v>716987</v>
       </c>
       <c r="R19" t="n">
-        <v>6374568</v>
+        <v>6374546</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2461,30 +2452,39 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2792,7 +2792,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128738844</v>
+        <v>128740480</v>
       </c>
       <c r="B23" t="n">
         <v>87039</v>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>717061</v>
+        <v>716999</v>
       </c>
       <c r="R23" t="n">
-        <v>6374502</v>
+        <v>6374513</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2860,19 +2860,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2887,19 +2877,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128740480</v>
+        <v>128738844</v>
       </c>
       <c r="B24" t="n">
         <v>87039</v>
@@ -2934,10 +2924,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>716999</v>
+        <v>717061</v>
       </c>
       <c r="R24" t="n">
-        <v>6374513</v>
+        <v>6374502</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2967,9 +2957,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2984,12 +2984,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -3400,7 +3400,7 @@
         <v>128738888</v>
       </c>
       <c r="B29" t="n">
-        <v>92834</v>
+        <v>92820</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
         <v>128738871</v>
       </c>
       <c r="B30" t="n">
-        <v>91075</v>
+        <v>91076</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -3400,7 +3400,7 @@
         <v>128738888</v>
       </c>
       <c r="B29" t="n">
-        <v>92820</v>
+        <v>92821</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -979,7 +979,7 @@
         <v>128742454</v>
       </c>
       <c r="B5" t="n">
-        <v>90337</v>
+        <v>90385</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -979,7 +979,7 @@
         <v>128742454</v>
       </c>
       <c r="B5" t="n">
-        <v>90385</v>
+        <v>90386</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -979,7 +979,7 @@
         <v>128742454</v>
       </c>
       <c r="B5" t="n">
-        <v>90386</v>
+        <v>90391</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -979,7 +979,7 @@
         <v>128742454</v>
       </c>
       <c r="B5" t="n">
-        <v>90391</v>
+        <v>90395</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -979,7 +979,7 @@
         <v>128742454</v>
       </c>
       <c r="B5" t="n">
-        <v>90395</v>
+        <v>90397</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -979,7 +979,7 @@
         <v>128742454</v>
       </c>
       <c r="B5" t="n">
-        <v>90397</v>
+        <v>90400</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -979,7 +979,7 @@
         <v>128742454</v>
       </c>
       <c r="B5" t="n">
-        <v>90400</v>
+        <v>90403</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -979,7 +979,7 @@
         <v>128742454</v>
       </c>
       <c r="B5" t="n">
-        <v>90403</v>
+        <v>90404</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -979,7 +979,7 @@
         <v>128742454</v>
       </c>
       <c r="B5" t="n">
-        <v>90404</v>
+        <v>90421</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128740515</v>
+        <v>128738868</v>
       </c>
       <c r="B2" t="n">
-        <v>92177</v>
+        <v>87368</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6031</v>
+        <v>449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717022</v>
+        <v>717048</v>
       </c>
       <c r="R2" t="n">
-        <v>6374547</v>
+        <v>6374524</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,9 +743,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,12 +770,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -775,7 +785,7 @@
         <v>128738869</v>
       </c>
       <c r="B3" t="n">
-        <v>87016</v>
+        <v>87368</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128740513</v>
+        <v>128740507</v>
       </c>
       <c r="B4" t="n">
-        <v>86819</v>
+        <v>87368</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3712</v>
+        <v>449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717090</v>
+        <v>717045</v>
       </c>
       <c r="R4" t="n">
-        <v>6374531</v>
+        <v>6374519</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,32 +986,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128742454</v>
+        <v>128738870</v>
       </c>
       <c r="B5" t="n">
-        <v>90436</v>
+        <v>91436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2072</v>
+        <v>1357</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1057,11 +1067,6 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Artbestämning bekräftad av Michael Krikorev.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,32 +1093,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128740493</v>
+        <v>128738871</v>
       </c>
       <c r="B6" t="n">
-        <v>86994</v>
+        <v>91436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6003295</v>
+        <v>1357</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717017</v>
+        <v>716991</v>
       </c>
       <c r="R6" t="n">
-        <v>6374570</v>
+        <v>6374543</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1156,83 +1161,84 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128742277</v>
+        <v>128738872</v>
       </c>
       <c r="B7" t="n">
-        <v>57648</v>
+        <v>91436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100001</v>
+        <v>1357</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717082</v>
+        <v>716991</v>
       </c>
       <c r="R7" t="n">
-        <v>6374502</v>
+        <v>6374537</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,14 +1268,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Slaktplats av nötskrika.</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1284,65 +1295,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128740488</v>
+        <v>128738874</v>
       </c>
       <c r="B8" t="n">
-        <v>57724</v>
+        <v>91436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1357</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717042</v>
+        <v>716987</v>
       </c>
       <c r="R8" t="n">
-        <v>6374557</v>
+        <v>6374546</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,9 +1375,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,57 +1402,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128740507</v>
+        <v>128738888</v>
       </c>
       <c r="B9" t="n">
-        <v>87016</v>
+        <v>93196</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>449</v>
+        <v>1435</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>717045</v>
+        <v>716959</v>
       </c>
       <c r="R9" t="n">
-        <v>6374519</v>
+        <v>6374567</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1469,61 +1485,77 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Luktar mandelkubb.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128738870</v>
+        <v>128742454</v>
       </c>
       <c r="B10" t="n">
-        <v>91075</v>
+        <v>90689</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1357</v>
+        <v>2072</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1579,6 +1611,11 @@
       <c r="AB10" t="inlineStr">
         <is>
           <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Artbestämning bekräftad av Michael Krikorev.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1605,32 +1642,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128740492</v>
+        <v>128740517</v>
       </c>
       <c r="B11" t="n">
-        <v>86994</v>
+        <v>87309</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1640,10 +1677,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>717123</v>
+        <v>716991</v>
       </c>
       <c r="R11" t="n">
-        <v>6374559</v>
+        <v>6374571</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,7 +1721,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1696,17 +1732,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128742292</v>
+        <v>128740520</v>
       </c>
       <c r="B12" t="n">
-        <v>86957</v>
+        <v>87309</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1738,10 +1774,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>717052</v>
+        <v>717104</v>
       </c>
       <c r="R12" t="n">
-        <v>6374546</v>
+        <v>6374483</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1763,7 +1799,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Anga</t>
+          <t>Kräklingbo</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1788,22 +1824,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128742260</v>
+        <v>128742292</v>
       </c>
       <c r="B13" t="n">
-        <v>91048</v>
+        <v>87309</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1811,21 +1847,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5741</v>
+        <v>3674</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1835,10 +1871,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716968</v>
+        <v>717052</v>
       </c>
       <c r="R13" t="n">
-        <v>6374553</v>
+        <v>6374546</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1897,32 +1933,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128740497</v>
+        <v>128742293</v>
       </c>
       <c r="B14" t="n">
-        <v>86994</v>
+        <v>87309</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6003295</v>
+        <v>3674</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1968,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>717081</v>
+        <v>717094</v>
       </c>
       <c r="R14" t="n">
-        <v>6374572</v>
+        <v>6374468</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1957,7 +1993,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Anga</t>
+          <t>Kräklingbo</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -1976,51 +2012,50 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128740483</v>
+        <v>128740513</v>
       </c>
       <c r="B15" t="n">
-        <v>87039</v>
+        <v>87170</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3767</v>
+        <v>3712</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2030,10 +2065,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>717059</v>
+        <v>717090</v>
       </c>
       <c r="R15" t="n">
-        <v>6374495</v>
+        <v>6374531</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2092,32 +2127,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128740481</v>
+        <v>128740490</v>
       </c>
       <c r="B16" t="n">
-        <v>87039</v>
+        <v>87146</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2127,10 +2162,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>717052</v>
+        <v>717075</v>
       </c>
       <c r="R16" t="n">
-        <v>6374557</v>
+        <v>6374568</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2189,32 +2224,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128740479</v>
+        <v>128742265</v>
       </c>
       <c r="B17" t="n">
-        <v>87039</v>
+        <v>87146</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3767</v>
+        <v>3762</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2224,10 +2259,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>717060</v>
+        <v>717052</v>
       </c>
       <c r="R17" t="n">
-        <v>6374568</v>
+        <v>6374544</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2268,51 +2303,50 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128740517</v>
+        <v>128738844</v>
       </c>
       <c r="B18" t="n">
-        <v>86957</v>
+        <v>87391</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2322,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716991</v>
+        <v>717061</v>
       </c>
       <c r="R18" t="n">
-        <v>6374571</v>
+        <v>6374502</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2355,9 +2389,19 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2372,22 +2416,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128738874</v>
+        <v>128740479</v>
       </c>
       <c r="B19" t="n">
-        <v>91075</v>
+        <v>87391</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2395,21 +2439,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1357</v>
+        <v>3767</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2419,10 +2463,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716987</v>
+        <v>717060</v>
       </c>
       <c r="R19" t="n">
-        <v>6374546</v>
+        <v>6374568</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2452,71 +2496,62 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128742265</v>
+        <v>128740480</v>
       </c>
       <c r="B20" t="n">
-        <v>86795</v>
+        <v>87391</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3762</v>
+        <v>3767</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2526,10 +2561,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>717052</v>
+        <v>716999</v>
       </c>
       <c r="R20" t="n">
-        <v>6374544</v>
+        <v>6374513</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2576,44 +2611,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128740490</v>
+        <v>128740481</v>
       </c>
       <c r="B21" t="n">
-        <v>86795</v>
+        <v>87391</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3762</v>
+        <v>3767</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2623,10 +2658,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>717075</v>
+        <v>717052</v>
       </c>
       <c r="R21" t="n">
-        <v>6374568</v>
+        <v>6374557</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2685,10 +2720,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128738868</v>
+        <v>128740483</v>
       </c>
       <c r="B22" t="n">
-        <v>87016</v>
+        <v>87391</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2696,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2720,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>717048</v>
+        <v>717059</v>
       </c>
       <c r="R22" t="n">
-        <v>6374524</v>
+        <v>6374495</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2753,19 +2788,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>15:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2780,44 +2805,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128740480</v>
+        <v>128742260</v>
       </c>
       <c r="B23" t="n">
-        <v>87039</v>
+        <v>91409</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3767</v>
+        <v>5741</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2827,10 +2852,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>716999</v>
+        <v>716968</v>
       </c>
       <c r="R23" t="n">
-        <v>6374513</v>
+        <v>6374553</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2877,44 +2902,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128738844</v>
+        <v>128740515</v>
       </c>
       <c r="B24" t="n">
-        <v>87039</v>
+        <v>92567</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3767</v>
+        <v>6031</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2924,10 +2949,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>717061</v>
+        <v>717022</v>
       </c>
       <c r="R24" t="n">
-        <v>6374502</v>
+        <v>6374547</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2957,19 +2982,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:09</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2984,22 +2999,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128740494</v>
+        <v>128742277</v>
       </c>
       <c r="B25" t="n">
-        <v>86994</v>
+        <v>57874</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3007,34 +3022,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6003295</v>
+        <v>100001</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>716964</v>
+        <v>717082</v>
       </c>
       <c r="R25" t="n">
-        <v>6374549</v>
+        <v>6374502</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3069,70 +3092,82 @@
           <t>2025-09-27</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Slaktplats av nötskrika.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128738872</v>
+        <v>128740488</v>
       </c>
       <c r="B26" t="n">
-        <v>91075</v>
+        <v>57950</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1357</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>716991</v>
+        <v>717042</v>
       </c>
       <c r="R26" t="n">
-        <v>6374537</v>
+        <v>6374557</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3162,19 +3197,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:03</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3189,22 +3214,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128740496</v>
+        <v>128740492</v>
       </c>
       <c r="B27" t="n">
-        <v>86994</v>
+        <v>87346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3236,10 +3261,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>717083</v>
+        <v>717123</v>
       </c>
       <c r="R27" t="n">
-        <v>6374544</v>
+        <v>6374559</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3299,10 +3324,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128740495</v>
+        <v>128740493</v>
       </c>
       <c r="B28" t="n">
-        <v>86994</v>
+        <v>87346</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3334,10 +3359,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>717014</v>
+        <v>717017</v>
       </c>
       <c r="R28" t="n">
-        <v>6374563</v>
+        <v>6374570</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3397,48 +3422,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128738888</v>
+        <v>128740494</v>
       </c>
       <c r="B29" t="n">
-        <v>92821</v>
+        <v>87346</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1435</v>
+        <v>6003295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Gurpe, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>716959</v>
+        <v>716964</v>
       </c>
       <c r="R29" t="n">
-        <v>6374567</v>
+        <v>6374549</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3468,24 +3490,9 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>15:58</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-09-27</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Luktar mandelkubb.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3501,44 +3508,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128738871</v>
+        <v>128740495</v>
       </c>
       <c r="B30" t="n">
-        <v>91076</v>
+        <v>87346</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1357</v>
+        <v>6003295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fläckfingersvamp</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramaria sanguinea</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Pers.) Quél.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3548,10 +3555,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>716991</v>
+        <v>717014</v>
       </c>
       <c r="R30" t="n">
-        <v>6374543</v>
+        <v>6374563</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3581,42 +3588,326 @@
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-09-27</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128740496</v>
+      </c>
+      <c r="B31" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Gurpe, Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>717083</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6374544</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128740497</v>
+      </c>
+      <c r="B32" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Gurpe, Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>717081</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6374572</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128740510</v>
+      </c>
+      <c r="B33" t="n">
+        <v>87312</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6037417</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Denisespindling</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Cortinarius olivaceodionysae</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>A.Ortega &amp; al.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Gurpe, Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>717105</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6374479</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Kräklingbo</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3226,10 +3226,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128740492</v>
+        <v>134675718</v>
       </c>
       <c r="B27" t="n">
-        <v>87346</v>
+        <v>43472</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3237,34 +3237,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6003295</v>
+        <v>101242</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Ange Sudebys, Gtl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>717123</v>
+        <v>716976</v>
       </c>
       <c r="R27" t="n">
-        <v>6374559</v>
+        <v>6374579</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3291,12 +3291,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3305,29 +3315,28 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128740493</v>
+        <v>134675720</v>
       </c>
       <c r="B28" t="n">
-        <v>87346</v>
+        <v>43472</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3335,37 +3344,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6003295</v>
+        <v>101242</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Ange Sudebys, Gtl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>717017</v>
+        <v>716996</v>
       </c>
       <c r="R28" t="n">
-        <v>6374570</v>
+        <v>6374565</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3389,12 +3398,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3403,29 +3422,28 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128740494</v>
+        <v>134675722</v>
       </c>
       <c r="B29" t="n">
-        <v>87346</v>
+        <v>43472</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3433,37 +3451,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6003295</v>
+        <v>101242</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Ange Sudebys, Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>716964</v>
+        <v>717011</v>
       </c>
       <c r="R29" t="n">
-        <v>6374549</v>
+        <v>6374563</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3487,12 +3505,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3501,29 +3529,28 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128740495</v>
+        <v>134675724</v>
       </c>
       <c r="B30" t="n">
-        <v>87346</v>
+        <v>43472</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3531,37 +3558,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6003295</v>
+        <v>101242</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Ange Sudebys, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>717014</v>
+        <v>717022</v>
       </c>
       <c r="R30" t="n">
-        <v>6374563</v>
+        <v>6374552</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3585,12 +3612,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3599,29 +3636,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128740496</v>
+        <v>134675725</v>
       </c>
       <c r="B31" t="n">
-        <v>87346</v>
+        <v>43472</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3629,37 +3665,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6003295</v>
+        <v>101242</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Ange Sudebys, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>717083</v>
+        <v>717033</v>
       </c>
       <c r="R31" t="n">
-        <v>6374544</v>
+        <v>6374554</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3683,12 +3719,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3697,29 +3743,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128740497</v>
+        <v>134675728</v>
       </c>
       <c r="B32" t="n">
-        <v>87346</v>
+        <v>43472</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3727,37 +3772,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6003295</v>
+        <v>101242</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Ange Sudebys, Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>717081</v>
+        <v>717055</v>
       </c>
       <c r="R32" t="n">
-        <v>6374572</v>
+        <v>6374558</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3781,12 +3826,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3795,29 +3850,28 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128740510</v>
+        <v>134675729</v>
       </c>
       <c r="B33" t="n">
-        <v>87312</v>
+        <v>43472</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3825,37 +3879,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6037417</v>
+        <v>101242</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Denisespindling</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius olivaceodionysae</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>A.Ortega &amp; al.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gurpe, Gtl</t>
+          <t>Ange Sudebys, Gtl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>717105</v>
+        <v>717046</v>
       </c>
       <c r="R33" t="n">
-        <v>6374479</v>
+        <v>6374565</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3874,17 +3928,27 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Kräklingbo</t>
+          <t>Anga</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3899,15 +3963,7790 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>134675731</v>
+      </c>
+      <c r="B34" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Ange Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>717065</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6374560</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>134675732</v>
+      </c>
+      <c r="B35" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Ange Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>717074</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6374558</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>134675734</v>
+      </c>
+      <c r="B36" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Ange Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>717081</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6374558</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>134675735</v>
+      </c>
+      <c r="B37" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Ange Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>717085</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6374567</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>134675737</v>
+      </c>
+      <c r="B38" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Ange Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>717090</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6374555</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>134675739</v>
+      </c>
+      <c r="B39" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Ange Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>717089</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6374525</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>134675740</v>
+      </c>
+      <c r="B40" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Ange Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>717159</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6374518</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>134675742</v>
+      </c>
+      <c r="B41" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Ange Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>717180</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6374524</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>134675744</v>
+      </c>
+      <c r="B42" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Ange Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>717194</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6374539</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>134675747</v>
+      </c>
+      <c r="B43" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Ange Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>717230</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6374506</v>
+      </c>
+      <c r="S43" t="n">
+        <v>6</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>134675750</v>
+      </c>
+      <c r="B44" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Ange Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>717303</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6374475</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>134675811</v>
+      </c>
+      <c r="B45" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Ange Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>717069</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6374482</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Kräklingbo</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>134675812</v>
+      </c>
+      <c r="B46" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Ange Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>716957</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6374572</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>134682833</v>
+      </c>
+      <c r="B47" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Anga Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>716983</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6374540</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>134682836</v>
+      </c>
+      <c r="B48" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Anga Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>717032</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6374515</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>134682837</v>
+      </c>
+      <c r="B49" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Anga Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>717043</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6374509</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>134682838</v>
+      </c>
+      <c r="B50" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Anga Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>717062</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6374509</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>134682840</v>
+      </c>
+      <c r="B51" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Anga Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>717064</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6374502</v>
+      </c>
+      <c r="S51" t="n">
+        <v>12</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>2st</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>134682841</v>
+      </c>
+      <c r="B52" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Anga Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>717084</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6374503</v>
+      </c>
+      <c r="S52" t="n">
+        <v>6</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>2st</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>134682844</v>
+      </c>
+      <c r="B53" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Anga Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>717096</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6374512</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>3st</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>134682845</v>
+      </c>
+      <c r="B54" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Anga Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>717092</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6374503</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>2st</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>134682846</v>
+      </c>
+      <c r="B55" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Anga Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>717088</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6374520</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>134682850</v>
+      </c>
+      <c r="B56" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Anga Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>717180</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6374515</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>134682854</v>
+      </c>
+      <c r="B57" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Anga Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>717190</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6374497</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>134682855</v>
+      </c>
+      <c r="B58" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Anga Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>717189</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6374510</v>
+      </c>
+      <c r="S58" t="n">
+        <v>6</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>134682857</v>
+      </c>
+      <c r="B59" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Anga Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>717201</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6374505</v>
+      </c>
+      <c r="S59" t="n">
+        <v>14</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>2st</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>134682858</v>
+      </c>
+      <c r="B60" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Anga Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>717186</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6374520</v>
+      </c>
+      <c r="S60" t="n">
+        <v>6</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>134682859</v>
+      </c>
+      <c r="B61" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Anga Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>717193</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6374531</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>2st</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>134682861</v>
+      </c>
+      <c r="B62" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Anga Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>717242</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6374490</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>134682874</v>
+      </c>
+      <c r="B63" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Anga Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>717154</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6374492</v>
+      </c>
+      <c r="S63" t="n">
+        <v>14</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>134682877</v>
+      </c>
+      <c r="B64" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Anga Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>717130</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6374467</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Kräklingbo</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>134682878</v>
+      </c>
+      <c r="B65" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Anga Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>717063</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6374465</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Kräklingbo</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>134682879</v>
+      </c>
+      <c r="B66" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Anga Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>717046</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6374472</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Kräklingbo</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>134682880</v>
+      </c>
+      <c r="B67" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Anga Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>717057</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6374482</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Kräklingbo</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>134682882</v>
+      </c>
+      <c r="B68" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Anga Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>717056</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6374474</v>
+      </c>
+      <c r="S68" t="n">
+        <v>17</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Kräklingbo</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>134682883</v>
+      </c>
+      <c r="B69" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Anga Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>717075</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6374479</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Kräklingbo</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>134682884</v>
+      </c>
+      <c r="B70" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Anga Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>717071</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6374494</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>134682887</v>
+      </c>
+      <c r="B71" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Anga Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>717053</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6374496</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>3st</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>134682888</v>
+      </c>
+      <c r="B72" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Anga Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>717029</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6374536</v>
+      </c>
+      <c r="S72" t="n">
+        <v>28</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>134682889</v>
+      </c>
+      <c r="B73" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Anga Sudebys, Gtl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>717010</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6374554</v>
+      </c>
+      <c r="S73" t="n">
+        <v>17</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Esmeralda  Svanberg</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>134685459</v>
+      </c>
+      <c r="B74" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Anga Suderby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>716948</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6374542</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>134685460</v>
+      </c>
+      <c r="B75" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Anga Suderby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>716997</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6374557</v>
+      </c>
+      <c r="S75" t="n">
+        <v>16</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>134685461</v>
+      </c>
+      <c r="B76" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Anga Suderby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>717004</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6374545</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>134685462</v>
+      </c>
+      <c r="B77" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Anga Suderby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>717009</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6374542</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>134685463</v>
+      </c>
+      <c r="B78" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Anga Suderby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>717017</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6374530</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>2 st</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>134685465</v>
+      </c>
+      <c r="B79" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Anga Suderby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>717037</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6374530</v>
+      </c>
+      <c r="S79" t="n">
+        <v>6</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>3 st</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>134685467</v>
+      </c>
+      <c r="B80" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Anga Suderby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>717062</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6374521</v>
+      </c>
+      <c r="S80" t="n">
+        <v>7</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>134685468</v>
+      </c>
+      <c r="B81" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Anga Suderby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>717080</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6374535</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>134685469</v>
+      </c>
+      <c r="B82" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Anga Suderby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>717081</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6374535</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>134685471</v>
+      </c>
+      <c r="B83" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Anga Suderby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>717095</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6374524</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>134685472</v>
+      </c>
+      <c r="B84" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Anga Suderby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>717088</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6374535</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>134685473</v>
+      </c>
+      <c r="B85" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Anga Suderby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>717163</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6374458</v>
+      </c>
+      <c r="S85" t="n">
+        <v>14</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Kräklingbo</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>134685474</v>
+      </c>
+      <c r="B86" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Anga Suderby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>717167</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6374485</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>134685478</v>
+      </c>
+      <c r="B87" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Anga Suderby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>717208</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6374486</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>134685479</v>
+      </c>
+      <c r="B88" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Anga Suderby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>717227</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6374495</v>
+      </c>
+      <c r="S88" t="n">
+        <v>6</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>2 st</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>134685481</v>
+      </c>
+      <c r="B89" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Anga Suderby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>717156</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6374482</v>
+      </c>
+      <c r="S89" t="n">
+        <v>5</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Kräklingbo</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>134685482</v>
+      </c>
+      <c r="B90" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Anga Suderby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>717066</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6374468</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Kräklingbo</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>134685486</v>
+      </c>
+      <c r="B91" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Anga Suderby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>717046</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6374468</v>
+      </c>
+      <c r="S91" t="n">
+        <v>5</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Kräklingbo</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>134685487</v>
+      </c>
+      <c r="B92" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Anga Suderby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>717046</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6374479</v>
+      </c>
+      <c r="S92" t="n">
+        <v>5</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Kräklingbo</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>134685488</v>
+      </c>
+      <c r="B93" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Anga Suderby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>717051</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6374486</v>
+      </c>
+      <c r="S93" t="n">
+        <v>5</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Kräklingbo</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>134685490</v>
+      </c>
+      <c r="B94" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Anga Suderby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>717080</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6374551</v>
+      </c>
+      <c r="S94" t="n">
+        <v>5</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>134685492</v>
+      </c>
+      <c r="B95" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Anga Suderby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>716992</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6374573</v>
+      </c>
+      <c r="S95" t="n">
+        <v>5</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>134685493</v>
+      </c>
+      <c r="B96" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Anga Suderby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>716986</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6374571</v>
+      </c>
+      <c r="S96" t="n">
+        <v>5</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>134685494</v>
+      </c>
+      <c r="B97" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Anga Suderby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>716985</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6374573</v>
+      </c>
+      <c r="S97" t="n">
+        <v>5</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>134685476</v>
+      </c>
+      <c r="B98" t="n">
+        <v>99230</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Anga Suderby, Gtl</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>717180</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6374484</v>
+      </c>
+      <c r="S98" t="n">
+        <v>5</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>128740492</v>
+      </c>
+      <c r="B99" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Gurpe, Gtl</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>717123</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6374559</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
           <t>Liam Sebestyén</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
+      <c r="AX99" t="inlineStr">
         <is>
           <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
         </is>
       </c>
-      <c r="AY33" t="inlineStr"/>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>128740493</v>
+      </c>
+      <c r="B100" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Gurpe, Gtl</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>717017</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6374570</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>128740494</v>
+      </c>
+      <c r="B101" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Gurpe, Gtl</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>716964</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6374549</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>128740495</v>
+      </c>
+      <c r="B102" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Gurpe, Gtl</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>717014</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6374563</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>128740496</v>
+      </c>
+      <c r="B103" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Gurpe, Gtl</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>717083</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6374544</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>128740497</v>
+      </c>
+      <c r="B104" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Gurpe, Gtl</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>717081</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6374572</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Anga</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF104" t="inlineStr"/>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>128740510</v>
+      </c>
+      <c r="B105" t="n">
+        <v>87312</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>6037417</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Denisespindling</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Cortinarius olivaceodionysae</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>A.Ortega &amp; al.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Gurpe, Gtl</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>717105</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6374479</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Kräklingbo</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-09-27</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Martin Axegård, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44204-2022 artfynd.xlsx
+++ b/artfynd/A 44204-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY105"/>
+  <dimension ref="A1:AZ105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128738868</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128738869</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128740507</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128738870</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128738871</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128738872</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128738874</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1527,6 +1567,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128738888</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1639,6 +1684,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128742454</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1736,6 +1786,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128740517</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1833,6 +1888,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128740520</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1930,6 +1990,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128742292</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2027,6 +2092,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128742293</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2124,6 +2194,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128740513</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2221,6 +2296,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128740490</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2318,6 +2398,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128742265</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2425,6 +2510,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128738844</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2523,6 +2613,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128740479</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2620,6 +2715,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128740480</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2717,6 +2817,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128740481</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2814,6 +2919,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128740483</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2911,6 +3021,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128742260</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3008,6 +3123,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128740515</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3118,6 +3238,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128742277</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3223,6 +3348,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128740488</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3330,6 +3460,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134675718</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3437,6 +3572,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134675720</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3544,6 +3684,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134675722</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3651,6 +3796,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134675724</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3758,6 +3908,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134675725</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3865,6 +4020,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134675728</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3972,6 +4132,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134675729</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4079,6 +4244,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134675731</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4186,6 +4356,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134675732</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4293,6 +4468,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134675734</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4400,6 +4580,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134675735</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4507,6 +4692,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134675737</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4614,6 +4804,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134675739</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4721,6 +4916,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134675740</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4828,6 +5028,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134675742</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4935,6 +5140,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134675744</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5042,6 +5252,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134675747</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5149,6 +5364,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134675750</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5256,6 +5476,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134675811</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5363,6 +5588,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134675812</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5475,6 +5705,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682833</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5587,6 +5822,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682836</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5699,6 +5939,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682837</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5811,6 +6056,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682838</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5923,6 +6173,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682840</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6035,6 +6290,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682841</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6147,6 +6407,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682844</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6259,6 +6524,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682845</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6371,6 +6641,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682846</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6483,6 +6758,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682850</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6595,6 +6875,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682854</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6707,6 +6992,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682855</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6819,6 +7109,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682857</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6931,6 +7226,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682858</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7043,6 +7343,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682859</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7155,6 +7460,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682861</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7267,6 +7577,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682874</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7379,6 +7694,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682877</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7486,6 +7806,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682878</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7593,6 +7918,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682879</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7700,6 +8030,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682880</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7812,6 +8147,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682882</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7924,6 +8264,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682883</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8036,6 +8381,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682884</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8148,6 +8498,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682887</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8260,6 +8615,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682888</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8372,6 +8732,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682889</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8479,6 +8844,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685459</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8586,6 +8956,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685460</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8693,6 +9068,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685461</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8800,6 +9180,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685462</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8912,6 +9297,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685463</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9024,6 +9414,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685465</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9131,6 +9526,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685467</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9238,6 +9638,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685468</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9345,6 +9750,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685469</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9452,6 +9862,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685471</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9559,6 +9974,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685472</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9666,6 +10086,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685473</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9773,6 +10198,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685474</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9880,6 +10310,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685478</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9992,6 +10427,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685479</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10099,6 +10539,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685481</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10206,6 +10651,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685482</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10313,6 +10763,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685486</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10420,6 +10875,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685487</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10527,6 +10987,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685488</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10634,6 +11099,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685490</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10741,6 +11211,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685492</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10848,6 +11323,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685493</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10955,6 +11435,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685494</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11062,6 +11547,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134685476</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11160,6 +11650,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128740492</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11258,6 +11753,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128740493</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11356,6 +11856,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128740494</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11454,6 +11959,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128740495</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11552,6 +12062,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128740496</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11650,6 +12165,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128740497</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11747,8 +12267,119 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128740510</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>